--- a/data-cleaning/verified/增量_2026年1号机C修_汇总展开91.xlsx
+++ b/data-cleaning/verified/增量_2026年1号机C修_汇总展开91.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F002-W064</t>
+          <t>1G-GGRQ-GQ-L001-F002-W</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-F003-W065</t>
+          <t>1G-GGRQ-GQ-L001-F003-W</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F002-W066</t>
+          <t>1G-GGRQ-GQ-L002-F002-W</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-F003-W067</t>
+          <t>1G-GGRQ-GQ-L002-F003-W</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F002-W068</t>
+          <t>1G-GGRQ-GQ-L003-F002-W</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-F003-W069</t>
+          <t>1G-GGRQ-GQ-L003-F003-W</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L004-F002-W070</t>
+          <t>1G-GGRQ-GQ-L004-F002-W</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-F003-W073</t>
+          <t>1G-GGRQ-GQ-L005-F003-W</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L006-F002-W074</t>
+          <t>1G-GGRQ-GQ-L006-F002-W</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L006-F003-W075</t>
+          <t>1G-GGRQ-GQ-L006-F003-W</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F002-W076</t>
+          <t>1G-GGRQ-GQ-L007-F002-W</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-F003-W077</t>
+          <t>1G-GGRQ-GQ-L007-F003-W</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L008-F002-W078</t>
+          <t>1G-GGRQ-GQ-L008-F002-W</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L008-F003-W079</t>
+          <t>1G-GGRQ-GQ-L008-F003-W</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L009-F002-W080</t>
+          <t>1G-GGRQ-GQ-L009-F002-W</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L009-F003-W081</t>
+          <t>1G-GGRQ-GQ-L009-F003-W</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L010-F003-W083</t>
+          <t>1G-GGRQ-GQ-L010-F003-W</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L011-F002-W084</t>
+          <t>1G-GGRQ-GQ-L011-F002-W</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L011-F003-W085</t>
+          <t>1G-GGRQ-GQ-L011-F003-W</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L012-F002-W086</t>
+          <t>1G-GGRQ-GQ-L012-F002-W</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L012-F003-W087</t>
+          <t>1G-GGRQ-GQ-L012-F003-W</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L013-F003-W089</t>
+          <t>1G-GGRQ-GQ-L013-F003-W</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L014-F002-W090</t>
+          <t>1G-GGRQ-GQ-L014-F002-W</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L014-F003-W091</t>
+          <t>1G-GGRQ-GQ-L014-F003-W</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L015-F002-W092</t>
+          <t>1G-GGRQ-GQ-L015-F002-W</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L015-F003-W093</t>
+          <t>1G-GGRQ-GQ-L015-F003-W</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L016-F002-W094</t>
+          <t>1G-GGRQ-GQ-L016-F002-W</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L016-F003-W095</t>
+          <t>1G-GGRQ-GQ-L016-F003-W</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L017-F002-W096</t>
+          <t>1G-GGRQ-GQ-L017-F002-W</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L017-F003-W097</t>
+          <t>1G-GGRQ-GQ-L017-F003-W</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L018-F002-W098</t>
+          <t>1G-GGRQ-GQ-L018-F002-W</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L018-F003-W099</t>
+          <t>1G-GGRQ-GQ-L018-F003-W</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L019-F002-W100</t>
+          <t>1G-GGRQ-GQ-L019-F002-W</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L019-F003-W101</t>
+          <t>1G-GGRQ-GQ-L019-F003-W</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L020-F002-W102</t>
+          <t>1G-GGRQ-GQ-L020-F002-W</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L020-F003-W103</t>
+          <t>1G-GGRQ-GQ-L020-F003-W</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L021-F002-W104</t>
+          <t>1G-GGRQ-GQ-L021-F002-W</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L021-F003-W105</t>
+          <t>1G-GGRQ-GQ-L021-F003-W</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L022-F002-W106</t>
+          <t>1G-GGRQ-GQ-L022-F002-W</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L022-F003-W107</t>
+          <t>1G-GGRQ-GQ-L022-F003-W</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L023-F002-W108</t>
+          <t>1G-GGRQ-GQ-L023-F002-W</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L023-F003-W109</t>
+          <t>1G-GGRQ-GQ-L023-F003-W</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L024-F002-W110</t>
+          <t>1G-GGRQ-GQ-L024-F002-W</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L024-F003-W111</t>
+          <t>1G-GGRQ-GQ-L024-F003-W</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L025-F003-W113</t>
+          <t>1G-GGRQ-GQ-L025-F003-W</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L026-F002-W114</t>
+          <t>1G-GGRQ-GQ-L026-F002-W</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L026-F003-W115</t>
+          <t>1G-GGRQ-GQ-L026-F003-W</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L027-F002-W116</t>
+          <t>1G-GGRQ-GQ-L027-F002-W</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L027-F003-W117</t>
+          <t>1G-GGRQ-GQ-L027-F003-W</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L028-F002-W118</t>
+          <t>1G-GGRQ-GQ-L028-F002-W</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L028-F003-W119</t>
+          <t>1G-GGRQ-GQ-L028-F003-W</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L029-F002-W120</t>
+          <t>1G-GGRQ-GQ-L029-F002-W</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L029-F003-W121</t>
+          <t>1G-GGRQ-GQ-L029-F003-W</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L030-F002-W122</t>
+          <t>1G-GGRQ-GQ-L030-F002-W</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L030-F003-W123</t>
+          <t>1G-GGRQ-GQ-L030-F003-W</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F002-W124</t>
+          <t>1G-GGRQ-GQ-L031-F002-W</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-F003-W125</t>
+          <t>1G-GGRQ-GQ-L031-F003-W</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L032-F002-W126</t>
+          <t>1G-GGRQ-GQ-L032-F002-W</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L032-F003-W127</t>
+          <t>1G-GGRQ-GQ-L032-F003-W</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-B001-W128</t>
+          <t>1G-GGRQ-GQ-L001-B001-W</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-B001-W129</t>
+          <t>1G-GGRQ-GQ-L002-B001-W</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-B001-W130</t>
+          <t>1G-GGRQ-GQ-L003-B001-W</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L004-B001-W131</t>
+          <t>1G-GGRQ-GQ-L004-B001-W</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-B001-W132</t>
+          <t>1G-GGRQ-GQ-L005-B001-W</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L006-B001-W133</t>
+          <t>1G-GGRQ-GQ-L006-B001-W</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-B001-W134</t>
+          <t>1G-GGRQ-GQ-L007-B001-W</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -6424,7 +6424,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L008-B001-W135</t>
+          <t>1G-GGRQ-GQ-L008-B001-W</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L009-B001-W136</t>
+          <t>1G-GGRQ-GQ-L009-B001-W</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L010-B001-W137</t>
+          <t>1G-GGRQ-GQ-L010-B001-W</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L011-B001-W138</t>
+          <t>1G-GGRQ-GQ-L011-B001-W</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L012-B001-W139</t>
+          <t>1G-GGRQ-GQ-L012-B001-W</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -6864,7 +6864,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L013-B001-W140</t>
+          <t>1G-GGRQ-GQ-L013-B001-W</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L014-B001-W141</t>
+          <t>1G-GGRQ-GQ-L014-B001-W</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L015-B001-W142</t>
+          <t>1G-GGRQ-GQ-L015-B001-W</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L016-B001-W143</t>
+          <t>1G-GGRQ-GQ-L016-B001-W</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L017-B001-W144</t>
+          <t>1G-GGRQ-GQ-L017-B001-W</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L018-B001-W145</t>
+          <t>1G-GGRQ-GQ-L018-B001-W</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L019-B001-W146</t>
+          <t>1G-GGRQ-GQ-L019-B001-W</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L020-B001-W147</t>
+          <t>1G-GGRQ-GQ-L020-B001-W</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -7568,7 +7568,7 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L021-B001-W148</t>
+          <t>1G-GGRQ-GQ-L021-B001-W</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
@@ -7656,7 +7656,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L022-B001-W149</t>
+          <t>1G-GGRQ-GQ-L022-B001-W</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L023-B001-W150</t>
+          <t>1G-GGRQ-GQ-L023-B001-W</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L024-B001-W151</t>
+          <t>1G-GGRQ-GQ-L024-B001-W</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L025-B001-W152</t>
+          <t>1G-GGRQ-GQ-L025-B001-W</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
@@ -8008,7 +8008,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L026-B001-W153</t>
+          <t>1G-GGRQ-GQ-L026-B001-W</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L027-B001-W154</t>
+          <t>1G-GGRQ-GQ-L027-B001-W</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -8184,7 +8184,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L028-B001-W155</t>
+          <t>1G-GGRQ-GQ-L028-B001-W</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -8272,7 +8272,7 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L029-B001-W156</t>
+          <t>1G-GGRQ-GQ-L029-B001-W</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L030-B001-W157</t>
+          <t>1G-GGRQ-GQ-L030-B001-W</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-B001-W158</t>
+          <t>1G-GGRQ-GQ-L031-B001-W</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L032-B001-W159</t>
+          <t>1G-GGRQ-GQ-L032-B001-W</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">

--- a/data-cleaning/verified/增量_2026年1号机C修_汇总展开91.xlsx
+++ b/data-cleaning/verified/增量_2026年1号机C修_汇总展开91.xlsx
@@ -639,7 +639,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#001；位置：L001-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#001；位置：L001-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       <c r="J3" s="4" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#002；位置：L001-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#002；位置：L001-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -815,7 +815,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#003；位置：L002-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#003；位置：L002-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#004；位置：L002-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#004；位置：L002-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -991,7 +991,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#005；位置：L003-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#005；位置：L003-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1079,7 +1079,7 @@
       <c r="J7" s="4" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#006；位置：L003-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#006；位置：L003-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1167,7 +1167,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#007；位置：L004-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#007；位置：L004-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       <c r="J9" s="4" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#010；位置：L005-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#010；位置：L005-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1343,7 +1343,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#011；位置：L006-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#011；位置：L006-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       <c r="J11" s="4" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#012；位置：L006-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#012；位置：L006-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1519,7 +1519,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#013；位置：L007-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#013；位置：L007-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1607,7 +1607,7 @@
       <c r="J13" s="4" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#014；位置：L007-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#014；位置：L007-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1695,7 +1695,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#015；位置：L008-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#015；位置：L008-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1783,7 +1783,7 @@
       <c r="J15" s="4" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#016；位置：L008-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#016；位置：L008-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1871,7 +1871,7 @@
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#017；位置：L009-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#017；位置：L009-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       <c r="J17" s="4" t="inlineStr"/>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#018；位置：L009-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#018；位置：L009-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#020；位置：L010-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#020；位置：L010-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2135,7 +2135,7 @@
       <c r="J19" s="4" t="inlineStr"/>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#021；位置：L011-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#021；位置：L011-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -2223,7 +2223,7 @@
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#022；位置：L011-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#022；位置：L011-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2311,7 +2311,7 @@
       <c r="J21" s="4" t="inlineStr"/>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#023；位置：L012-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#023；位置：L012-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -2399,7 +2399,7 @@
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#024；位置：L012-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#024；位置：L012-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       <c r="J23" s="4" t="inlineStr"/>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#026；位置：L013-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#026；位置：L013-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -2575,7 +2575,7 @@
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#027；位置：L014-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#027；位置：L014-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       <c r="J25" s="4" t="inlineStr"/>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#028；位置：L014-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#028；位置：L014-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -2751,7 +2751,7 @@
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#029；位置：L015-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#029；位置：L015-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -2839,7 +2839,7 @@
       <c r="J27" s="4" t="inlineStr"/>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#030；位置：L015-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#030；位置：L015-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -2927,7 +2927,7 @@
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#031；位置：L016-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#031；位置：L016-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -3015,7 +3015,7 @@
       <c r="J29" s="4" t="inlineStr"/>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#032；位置：L016-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#032；位置：L016-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -3103,7 +3103,7 @@
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#033；位置：L017-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#033；位置：L017-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3191,7 +3191,7 @@
       <c r="J31" s="4" t="inlineStr"/>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#034；位置：L017-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#034；位置：L017-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -3279,7 +3279,7 @@
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#035；位置：L018-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#035；位置：L018-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3367,7 +3367,7 @@
       <c r="J33" s="4" t="inlineStr"/>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#036；位置：L018-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#036；位置：L018-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -3455,7 +3455,7 @@
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#037；位置：L019-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#037；位置：L019-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -3543,7 +3543,7 @@
       <c r="J35" s="4" t="inlineStr"/>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#038；位置：L019-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#038；位置：L019-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -3631,7 +3631,7 @@
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#039；位置：L020-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#039；位置：L020-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -3719,7 +3719,7 @@
       <c r="J37" s="4" t="inlineStr"/>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#040；位置：L020-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#040；位置：L020-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -3807,7 +3807,7 @@
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#041；位置：L021-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#041；位置：L021-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -3895,7 +3895,7 @@
       <c r="J39" s="4" t="inlineStr"/>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#042；位置：L021-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#042；位置：L021-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -3983,7 +3983,7 @@
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#043；位置：L022-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#043；位置：L022-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       <c r="J41" s="4" t="inlineStr"/>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#044；位置：L022-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#044；位置：L022-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -4159,7 +4159,7 @@
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#045；位置：L023-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#045；位置：L023-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -4247,7 +4247,7 @@
       <c r="J43" s="4" t="inlineStr"/>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#046；位置：L023-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#046；位置：L023-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -4335,7 +4335,7 @@
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#047；位置：L024-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#047；位置：L024-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -4423,7 +4423,7 @@
       <c r="J45" s="4" t="inlineStr"/>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#048；位置：L024-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#048；位置：L024-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -4511,7 +4511,7 @@
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#050；位置：L025-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#050；位置：L025-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -4599,7 +4599,7 @@
       <c r="J47" s="4" t="inlineStr"/>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#051；位置：L026-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#051；位置：L026-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -4687,7 +4687,7 @@
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#052；位置：L026-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#052；位置：L026-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       <c r="J49" s="4" t="inlineStr"/>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#053；位置：L027-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#053；位置：L027-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -4863,7 +4863,7 @@
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#054；位置：L027-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#054；位置：L027-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -4951,7 +4951,7 @@
       <c r="J51" s="4" t="inlineStr"/>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#055；位置：L028-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#055；位置：L028-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -5039,7 +5039,7 @@
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#056；位置：L028-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#056；位置：L028-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -5127,7 +5127,7 @@
       <c r="J53" s="4" t="inlineStr"/>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#057；位置：L029-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#057；位置：L029-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -5215,7 +5215,7 @@
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#058；位置：L029-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#058；位置：L029-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -5303,7 +5303,7 @@
       <c r="J55" s="4" t="inlineStr"/>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#059；位置：L030-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#059；位置：L030-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -5391,7 +5391,7 @@
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#060；位置：L030-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#060；位置：L030-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -5479,7 +5479,7 @@
       <c r="J57" s="4" t="inlineStr"/>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#061；位置：L031-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#061；位置：L031-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -5567,7 +5567,7 @@
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#062；位置：L031-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#062；位置：L031-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -5655,7 +5655,7 @@
       <c r="J59" s="4" t="inlineStr"/>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#063；位置：L032-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#063；位置：L032-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -5743,7 +5743,7 @@
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#064；位置：L032-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；与其他行候选对应关系有疑点，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#064；位置：L032-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L001-B001-W</t>
+          <t>1G-GGRQ-GQ-L001-F024-W</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -5831,7 +5831,7 @@
       <c r="J61" s="4" t="inlineStr"/>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#001；位置：L001-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#001；位置：L001-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L002-B001-W</t>
+          <t>1G-GGRQ-GQ-L002-F024-W</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -5919,7 +5919,7 @@
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#002；位置：L002-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#002；位置：L002-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L003-B001-W</t>
+          <t>1G-GGRQ-GQ-L003-F024-W</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -6007,7 +6007,7 @@
       <c r="J63" s="4" t="inlineStr"/>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#003；位置：L003-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#003；位置：L003-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L004-B001-W</t>
+          <t>1G-GGRQ-GQ-L004-F024-W</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -6095,7 +6095,7 @@
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#004；位置：L004-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#004；位置：L004-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L005-B001-W</t>
+          <t>1G-GGRQ-GQ-L005-F024-W</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -6183,7 +6183,7 @@
       <c r="J65" s="4" t="inlineStr"/>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#005；位置：L005-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#005；位置：L005-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L006-B001-W</t>
+          <t>1G-GGRQ-GQ-L006-F024-W</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -6271,7 +6271,7 @@
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#006；位置：L006-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#006；位置：L006-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L007-B001-W</t>
+          <t>1G-GGRQ-GQ-L007-F024-W</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -6359,7 +6359,7 @@
       <c r="J67" s="4" t="inlineStr"/>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#007；位置：L007-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#007；位置：L007-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -6424,7 +6424,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L008-B001-W</t>
+          <t>1G-GGRQ-GQ-L008-F024-W</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -6447,7 +6447,7 @@
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#008；位置：L008-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#008；位置：L008-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L009-B001-W</t>
+          <t>1G-GGRQ-GQ-L009-F024-W</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -6535,7 +6535,7 @@
       <c r="J69" s="4" t="inlineStr"/>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#009；位置：L009-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#009；位置：L009-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L010-B001-W</t>
+          <t>1G-GGRQ-GQ-L010-F024-W</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -6623,7 +6623,7 @@
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#010；位置：L010-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#010；位置：L010-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L011-B001-W</t>
+          <t>1G-GGRQ-GQ-L011-F024-W</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -6711,7 +6711,7 @@
       <c r="J71" s="4" t="inlineStr"/>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#011；位置：L011-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#011；位置：L011-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L012-B001-W</t>
+          <t>1G-GGRQ-GQ-L012-F024-W</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -6799,7 +6799,7 @@
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#012；位置：L012-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#012；位置：L012-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
@@ -6864,7 +6864,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L013-B001-W</t>
+          <t>1G-GGRQ-GQ-L013-F024-W</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -6887,7 +6887,7 @@
       <c r="J73" s="4" t="inlineStr"/>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#013；位置：L013-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#013；位置：L013-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L014-B001-W</t>
+          <t>1G-GGRQ-GQ-L014-F024-W</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -6975,7 +6975,7 @@
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#014；位置：L014-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#014；位置：L014-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L015-B001-W</t>
+          <t>1G-GGRQ-GQ-L015-F024-W</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -7063,7 +7063,7 @@
       <c r="J75" s="4" t="inlineStr"/>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#015；位置：L015-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#015；位置：L015-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L016-B001-W</t>
+          <t>1G-GGRQ-GQ-L016-F024-W</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -7151,7 +7151,7 @@
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#016；位置：L016-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#016；位置：L016-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L017-B001-W</t>
+          <t>1G-GGRQ-GQ-L017-F024-W</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -7239,7 +7239,7 @@
       <c r="J77" s="4" t="inlineStr"/>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#017；位置：L017-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#017；位置：L017-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L018-B001-W</t>
+          <t>1G-GGRQ-GQ-L018-F024-W</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -7327,7 +7327,7 @@
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#018；位置：L018-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#018；位置：L018-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L019-B001-W</t>
+          <t>1G-GGRQ-GQ-L019-F024-W</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
@@ -7415,7 +7415,7 @@
       <c r="J79" s="4" t="inlineStr"/>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#019；位置：L019-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#019；位置：L019-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L020-B001-W</t>
+          <t>1G-GGRQ-GQ-L020-F024-W</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -7503,7 +7503,7 @@
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#020；位置：L020-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#020；位置：L020-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
@@ -7568,7 +7568,7 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L021-B001-W</t>
+          <t>1G-GGRQ-GQ-L021-F024-W</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
@@ -7591,7 +7591,7 @@
       <c r="J81" s="4" t="inlineStr"/>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#021；位置：L021-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#021；位置：L021-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
@@ -7656,7 +7656,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L022-B001-W</t>
+          <t>1G-GGRQ-GQ-L022-F024-W</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -7679,7 +7679,7 @@
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#022；位置：L022-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#022；位置：L022-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L023-B001-W</t>
+          <t>1G-GGRQ-GQ-L023-F024-W</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
@@ -7767,7 +7767,7 @@
       <c r="J83" s="4" t="inlineStr"/>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#023；位置：L023-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#023；位置：L023-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L024-B001-W</t>
+          <t>1G-GGRQ-GQ-L024-F024-W</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -7855,7 +7855,7 @@
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#024；位置：L024-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#024；位置：L024-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L025-B001-W</t>
+          <t>1G-GGRQ-GQ-L025-F024-W</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
@@ -7943,7 +7943,7 @@
       <c r="J85" s="4" t="inlineStr"/>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#025；位置：L025-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#025；位置：L025-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
@@ -8008,7 +8008,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L026-B001-W</t>
+          <t>1G-GGRQ-GQ-L026-F024-W</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -8031,7 +8031,7 @@
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#026；位置：L026-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#026；位置：L026-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L027-B001-W</t>
+          <t>1G-GGRQ-GQ-L027-F024-W</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -8119,7 +8119,7 @@
       <c r="J87" s="4" t="inlineStr"/>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#027；位置：L027-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#027；位置：L027-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
@@ -8184,7 +8184,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L028-B001-W</t>
+          <t>1G-GGRQ-GQ-L028-F024-W</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -8207,7 +8207,7 @@
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#028；位置：L028-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#028；位置：L028-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
@@ -8272,7 +8272,7 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L029-B001-W</t>
+          <t>1G-GGRQ-GQ-L029-F024-W</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -8295,7 +8295,7 @@
       <c r="J89" s="4" t="inlineStr"/>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#029；位置：L029-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#029；位置：L029-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L030-B001-W</t>
+          <t>1G-GGRQ-GQ-L030-F024-W</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -8383,7 +8383,7 @@
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#030；位置：L030-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#030；位置：L030-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L031-B001-W</t>
+          <t>1G-GGRQ-GQ-L031-F024-W</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
@@ -8471,7 +8471,7 @@
       <c r="J91" s="4" t="inlineStr"/>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#031；位置：L031-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#031；位置：L031-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>1G-GGRQ-GQ-L032-B001-W</t>
+          <t>1G-GGRQ-GQ-L032-F024-W</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -8559,7 +8559,7 @@
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#032；位置：L032-B001；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；保留炉后计数B001；每屏物理管总数未知，不反算为F024或F022</t>
+          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#032；位置：L032-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">

--- a/data-cleaning/verified/增量_2026年1号机C修_汇总展开91.xlsx
+++ b/data-cleaning/verified/增量_2026年1号机C修_汇总展开91.xlsx
@@ -469,7 +469,7 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="37" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
@@ -600,7 +600,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="107" customHeight="1">
+    <row r="2" ht="88" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -611,7 +611,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -639,7 +639,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#001；位置：L001-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#001；位置：L001-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="V2" s="2" t="inlineStr"/>
     </row>
-    <row r="3" ht="107" customHeight="1">
+    <row r="3" ht="88" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -699,7 +699,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
@@ -727,7 +727,7 @@
       <c r="J3" s="4" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#002；位置：L001-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#002；位置：L001-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -752,7 +752,7 @@
         <v>2</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="R3" s="4" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
       </c>
       <c r="S3" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T3" s="4" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="V3" s="4" t="inlineStr"/>
     </row>
-    <row r="4" ht="107" customHeight="1">
+    <row r="4" ht="88" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -787,7 +787,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
@@ -815,7 +815,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#003；位置：L002-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#003；位置：L002-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
         <v>3</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr"/>
     </row>
-    <row r="5" ht="107" customHeight="1">
+    <row r="5" ht="88" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -875,7 +875,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
@@ -903,7 +903,7 @@
       <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#004；位置：L002-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#004；位置：L002-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -928,7 +928,7 @@
         <v>4</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R5" s="4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
       </c>
       <c r="S5" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T5" s="4" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="V5" s="4" t="inlineStr"/>
     </row>
-    <row r="6" ht="107" customHeight="1">
+    <row r="6" ht="88" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -963,7 +963,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -991,7 +991,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#005；位置：L003-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#005；位置：L003-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1016,7 +1016,7 @@
         <v>5</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr"/>
     </row>
-    <row r="7" ht="107" customHeight="1">
+    <row r="7" ht="88" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
@@ -1079,7 +1079,7 @@
       <c r="J7" s="4" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#006；位置：L003-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#006；位置：L003-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1104,7 +1104,7 @@
         <v>6</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R7" s="4" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T7" s="4" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="V7" s="4" t="inlineStr"/>
     </row>
-    <row r="8" ht="107" customHeight="1">
+    <row r="8" ht="88" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -1167,7 +1167,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#007；位置：L004-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#007；位置：L004-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
         <v>7</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr"/>
     </row>
-    <row r="9" ht="107" customHeight="1">
+    <row r="9" ht="88" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
@@ -1255,7 +1255,7 @@
       <c r="J9" s="4" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#010；位置：L005-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#010；位置：L005-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1280,7 +1280,7 @@
         <v>10</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T9" s="4" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="V9" s="4" t="inlineStr"/>
     </row>
-    <row r="10" ht="107" customHeight="1">
+    <row r="10" ht="88" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -1343,7 +1343,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#011；位置：L006-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#011；位置：L006-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1368,7 +1368,7 @@
         <v>11</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr"/>
     </row>
-    <row r="11" ht="107" customHeight="1">
+    <row r="11" ht="88" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr"/>
@@ -1431,7 +1431,7 @@
       <c r="J11" s="4" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#012；位置：L006-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#012；位置：L006-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1456,7 +1456,7 @@
         <v>12</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="R11" s="4" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T11" s="4" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="V11" s="4" t="inlineStr"/>
     </row>
-    <row r="12" ht="107" customHeight="1">
+    <row r="12" ht="88" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -1519,7 +1519,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#013；位置：L007-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#013；位置：L007-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
         <v>13</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr"/>
     </row>
-    <row r="13" ht="107" customHeight="1">
+    <row r="13" ht="88" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr"/>
@@ -1607,7 +1607,7 @@
       <c r="J13" s="4" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#014；位置：L007-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#014；位置：L007-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1632,7 +1632,7 @@
         <v>14</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="S13" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T13" s="4" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="V13" s="4" t="inlineStr"/>
     </row>
-    <row r="14" ht="107" customHeight="1">
+    <row r="14" ht="88" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
@@ -1695,7 +1695,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#015；位置：L008-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#015；位置：L008-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1720,7 +1720,7 @@
         <v>15</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr"/>
     </row>
-    <row r="15" ht="107" customHeight="1">
+    <row r="15" ht="88" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr"/>
@@ -1783,7 +1783,7 @@
       <c r="J15" s="4" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#016；位置：L008-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#016；位置：L008-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1808,7 +1808,7 @@
         <v>16</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T15" s="4" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="V15" s="4" t="inlineStr"/>
     </row>
-    <row r="16" ht="107" customHeight="1">
+    <row r="16" ht="88" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
@@ -1871,7 +1871,7 @@
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#017；位置：L009-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#017；位置：L009-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1896,7 +1896,7 @@
         <v>17</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr"/>
     </row>
-    <row r="17" ht="107" customHeight="1">
+    <row r="17" ht="88" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr"/>
@@ -1959,7 +1959,7 @@
       <c r="J17" s="4" t="inlineStr"/>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#018；位置：L009-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#018；位置：L009-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1984,7 +1984,7 @@
         <v>18</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T17" s="4" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="V17" s="4" t="inlineStr"/>
     </row>
-    <row r="18" ht="107" customHeight="1">
+    <row r="18" ht="88" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
@@ -2047,7 +2047,7 @@
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#020；位置：L010-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#020；位置：L010-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2072,7 +2072,7 @@
         <v>20</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr"/>
     </row>
-    <row r="19" ht="107" customHeight="1">
+    <row r="19" ht="88" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr"/>
@@ -2135,7 +2135,7 @@
       <c r="J19" s="4" t="inlineStr"/>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#021；位置：L011-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#021；位置：L011-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -2160,7 +2160,7 @@
         <v>21</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T19" s="4" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="V19" s="4" t="inlineStr"/>
     </row>
-    <row r="20" ht="107" customHeight="1">
+    <row r="20" ht="88" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -2223,7 +2223,7 @@
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#022；位置：L011-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#022；位置：L011-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2248,7 +2248,7 @@
         <v>22</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr"/>
     </row>
-    <row r="21" ht="107" customHeight="1">
+    <row r="21" ht="88" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr"/>
@@ -2311,7 +2311,7 @@
       <c r="J21" s="4" t="inlineStr"/>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#023；位置：L012-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#023；位置：L012-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -2336,7 +2336,7 @@
         <v>23</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T21" s="4" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="V21" s="4" t="inlineStr"/>
     </row>
-    <row r="22" ht="107" customHeight="1">
+    <row r="22" ht="88" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
@@ -2399,7 +2399,7 @@
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#024；位置：L012-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#024；位置：L012-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2424,7 +2424,7 @@
         <v>24</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr"/>
     </row>
-    <row r="23" ht="107" customHeight="1">
+    <row r="23" ht="88" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr"/>
@@ -2487,7 +2487,7 @@
       <c r="J23" s="4" t="inlineStr"/>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#026；位置：L013-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#026；位置：L013-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -2512,7 +2512,7 @@
         <v>26</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T23" s="4" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="V23" s="4" t="inlineStr"/>
     </row>
-    <row r="24" ht="107" customHeight="1">
+    <row r="24" ht="88" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
@@ -2575,7 +2575,7 @@
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#027；位置：L014-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#027；位置：L014-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -2600,7 +2600,7 @@
         <v>27</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr"/>
     </row>
-    <row r="25" ht="107" customHeight="1">
+    <row r="25" ht="88" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr"/>
@@ -2663,7 +2663,7 @@
       <c r="J25" s="4" t="inlineStr"/>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#028；位置：L014-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#028；位置：L014-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -2688,7 +2688,7 @@
         <v>28</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T25" s="4" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="V25" s="4" t="inlineStr"/>
     </row>
-    <row r="26" ht="107" customHeight="1">
+    <row r="26" ht="88" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
@@ -2751,7 +2751,7 @@
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#029；位置：L015-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#029；位置：L015-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -2776,7 +2776,7 @@
         <v>29</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr"/>
     </row>
-    <row r="27" ht="107" customHeight="1">
+    <row r="27" ht="88" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr"/>
@@ -2839,7 +2839,7 @@
       <c r="J27" s="4" t="inlineStr"/>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#030；位置：L015-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#030；位置：L015-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -2864,7 +2864,7 @@
         <v>30</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="R27" s="4" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="S27" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T27" s="4" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="V27" s="4" t="inlineStr"/>
     </row>
-    <row r="28" ht="107" customHeight="1">
+    <row r="28" ht="88" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
@@ -2927,7 +2927,7 @@
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#031；位置：L016-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#031；位置：L016-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -2952,7 +2952,7 @@
         <v>31</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr"/>
     </row>
-    <row r="29" ht="107" customHeight="1">
+    <row r="29" ht="88" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr"/>
@@ -3015,7 +3015,7 @@
       <c r="J29" s="4" t="inlineStr"/>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#032；位置：L016-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#032；位置：L016-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -3040,7 +3040,7 @@
         <v>32</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="R29" s="4" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="S29" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T29" s="4" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="V29" s="4" t="inlineStr"/>
     </row>
-    <row r="30" ht="107" customHeight="1">
+    <row r="30" ht="88" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
@@ -3103,7 +3103,7 @@
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#033；位置：L017-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#033；位置：L017-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3128,7 +3128,7 @@
         <v>33</v>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr"/>
     </row>
-    <row r="31" ht="107" customHeight="1">
+    <row r="31" ht="88" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr"/>
@@ -3191,7 +3191,7 @@
       <c r="J31" s="4" t="inlineStr"/>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#034；位置：L017-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#034；位置：L017-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -3216,7 +3216,7 @@
         <v>34</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="R31" s="4" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S31" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T31" s="4" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="V31" s="4" t="inlineStr"/>
     </row>
-    <row r="32" ht="107" customHeight="1">
+    <row r="32" ht="88" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
@@ -3279,7 +3279,7 @@
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#035；位置：L018-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#035；位置：L018-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3304,7 +3304,7 @@
         <v>35</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr"/>
     </row>
-    <row r="33" ht="107" customHeight="1">
+    <row r="33" ht="88" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr"/>
@@ -3367,7 +3367,7 @@
       <c r="J33" s="4" t="inlineStr"/>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#036；位置：L018-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#036；位置：L018-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -3392,7 +3392,7 @@
         <v>36</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="R33" s="4" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="S33" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T33" s="4" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="V33" s="4" t="inlineStr"/>
     </row>
-    <row r="34" ht="107" customHeight="1">
+    <row r="34" ht="88" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3427,7 +3427,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
@@ -3455,7 +3455,7 @@
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#037；位置：L019-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#037；位置：L019-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
         <v>37</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr"/>
     </row>
-    <row r="35" ht="107" customHeight="1">
+    <row r="35" ht="88" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr"/>
@@ -3543,7 +3543,7 @@
       <c r="J35" s="4" t="inlineStr"/>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#038；位置：L019-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#038；位置：L019-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -3568,7 +3568,7 @@
         <v>38</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="R35" s="4" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="S35" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T35" s="4" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="V35" s="4" t="inlineStr"/>
     </row>
-    <row r="36" ht="107" customHeight="1">
+    <row r="36" ht="88" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
@@ -3631,7 +3631,7 @@
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#039；位置：L020-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#039；位置：L020-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -3656,7 +3656,7 @@
         <v>39</v>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr"/>
     </row>
-    <row r="37" ht="107" customHeight="1">
+    <row r="37" ht="88" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr"/>
@@ -3719,7 +3719,7 @@
       <c r="J37" s="4" t="inlineStr"/>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#040；位置：L020-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#040；位置：L020-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -3744,7 +3744,7 @@
         <v>40</v>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="R37" s="4" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="S37" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T37" s="4" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="V37" s="4" t="inlineStr"/>
     </row>
-    <row r="38" ht="107" customHeight="1">
+    <row r="38" ht="88" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
@@ -3807,7 +3807,7 @@
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#041；位置：L021-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#041；位置：L021-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -3832,7 +3832,7 @@
         <v>41</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="V38" s="2" t="inlineStr"/>
     </row>
-    <row r="39" ht="107" customHeight="1">
+    <row r="39" ht="88" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr"/>
@@ -3895,7 +3895,7 @@
       <c r="J39" s="4" t="inlineStr"/>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#042；位置：L021-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#042；位置：L021-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -3920,7 +3920,7 @@
         <v>42</v>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="R39" s="4" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="S39" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T39" s="4" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="V39" s="4" t="inlineStr"/>
     </row>
-    <row r="40" ht="107" customHeight="1">
+    <row r="40" ht="88" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
@@ -3983,7 +3983,7 @@
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#043；位置：L022-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#043；位置：L022-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -4008,7 +4008,7 @@
         <v>43</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="V40" s="2" t="inlineStr"/>
     </row>
-    <row r="41" ht="107" customHeight="1">
+    <row r="41" ht="88" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr"/>
@@ -4071,7 +4071,7 @@
       <c r="J41" s="4" t="inlineStr"/>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#044；位置：L022-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#044；位置：L022-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -4096,7 +4096,7 @@
         <v>44</v>
       </c>
       <c r="Q41" s="4" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="R41" s="4" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T41" s="4" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="V41" s="4" t="inlineStr"/>
     </row>
-    <row r="42" ht="107" customHeight="1">
+    <row r="42" ht="88" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
@@ -4159,7 +4159,7 @@
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#045；位置：L023-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#045；位置：L023-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
         <v>45</v>
       </c>
       <c r="Q42" s="2" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="V42" s="2" t="inlineStr"/>
     </row>
-    <row r="43" ht="107" customHeight="1">
+    <row r="43" ht="88" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr"/>
@@ -4247,7 +4247,7 @@
       <c r="J43" s="4" t="inlineStr"/>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#046；位置：L023-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#046；位置：L023-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -4272,7 +4272,7 @@
         <v>46</v>
       </c>
       <c r="Q43" s="4" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="R43" s="4" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
       </c>
       <c r="S43" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T43" s="4" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="V43" s="4" t="inlineStr"/>
     </row>
-    <row r="44" ht="107" customHeight="1">
+    <row r="44" ht="88" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4307,7 +4307,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
@@ -4335,7 +4335,7 @@
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#047；位置：L024-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#047；位置：L024-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -4360,7 +4360,7 @@
         <v>47</v>
       </c>
       <c r="Q44" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="V44" s="2" t="inlineStr"/>
     </row>
-    <row r="45" ht="107" customHeight="1">
+    <row r="45" ht="88" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr"/>
@@ -4423,7 +4423,7 @@
       <c r="J45" s="4" t="inlineStr"/>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#048；位置：L024-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#048；位置：L024-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -4448,7 +4448,7 @@
         <v>48</v>
       </c>
       <c r="Q45" s="4" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="R45" s="4" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T45" s="4" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="V45" s="4" t="inlineStr"/>
     </row>
-    <row r="46" ht="107" customHeight="1">
+    <row r="46" ht="88" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4483,7 +4483,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
@@ -4511,7 +4511,7 @@
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#050；位置：L025-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#050；位置：L025-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
         <v>50</v>
       </c>
       <c r="Q46" s="2" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="V46" s="2" t="inlineStr"/>
     </row>
-    <row r="47" ht="107" customHeight="1">
+    <row r="47" ht="88" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4571,7 +4571,7 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr"/>
@@ -4599,7 +4599,7 @@
       <c r="J47" s="4" t="inlineStr"/>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#051；位置：L026-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#051；位置：L026-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -4624,7 +4624,7 @@
         <v>51</v>
       </c>
       <c r="Q47" s="4" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="R47" s="4" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="S47" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T47" s="4" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="V47" s="4" t="inlineStr"/>
     </row>
-    <row r="48" ht="107" customHeight="1">
+    <row r="48" ht="88" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4659,7 +4659,7 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
@@ -4687,7 +4687,7 @@
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#052；位置：L026-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#052；位置：L026-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -4712,7 +4712,7 @@
         <v>52</v>
       </c>
       <c r="Q48" s="2" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="V48" s="2" t="inlineStr"/>
     </row>
-    <row r="49" ht="107" customHeight="1">
+    <row r="49" ht="88" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr"/>
@@ -4775,7 +4775,7 @@
       <c r="J49" s="4" t="inlineStr"/>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#053；位置：L027-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#053；位置：L027-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -4800,7 +4800,7 @@
         <v>53</v>
       </c>
       <c r="Q49" s="4" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="R49" s="4" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="S49" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T49" s="4" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V49" s="4" t="inlineStr"/>
     </row>
-    <row r="50" ht="107" customHeight="1">
+    <row r="50" ht="88" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr"/>
@@ -4863,7 +4863,7 @@
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#054；位置：L027-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#054；位置：L027-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
         <v>54</v>
       </c>
       <c r="Q50" s="2" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="V50" s="2" t="inlineStr"/>
     </row>
-    <row r="51" ht="107" customHeight="1">
+    <row r="51" ht="88" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr"/>
@@ -4951,7 +4951,7 @@
       <c r="J51" s="4" t="inlineStr"/>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#055；位置：L028-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#055；位置：L028-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -4976,7 +4976,7 @@
         <v>55</v>
       </c>
       <c r="Q51" s="4" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="R51" s="4" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
       </c>
       <c r="S51" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T51" s="4" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="V51" s="4" t="inlineStr"/>
     </row>
-    <row r="52" ht="107" customHeight="1">
+    <row r="52" ht="88" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr"/>
@@ -5039,7 +5039,7 @@
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#056；位置：L028-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#056；位置：L028-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
         <v>56</v>
       </c>
       <c r="Q52" s="2" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="V52" s="2" t="inlineStr"/>
     </row>
-    <row r="53" ht="107" customHeight="1">
+    <row r="53" ht="88" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5099,7 +5099,7 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr"/>
@@ -5127,7 +5127,7 @@
       <c r="J53" s="4" t="inlineStr"/>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#057；位置：L029-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#057；位置：L029-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -5152,7 +5152,7 @@
         <v>57</v>
       </c>
       <c r="Q53" s="4" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="R53" s="4" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="S53" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T53" s="4" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="V53" s="4" t="inlineStr"/>
     </row>
-    <row r="54" ht="107" customHeight="1">
+    <row r="54" ht="88" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
@@ -5215,7 +5215,7 @@
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#058；位置：L029-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#058；位置：L029-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -5240,7 +5240,7 @@
         <v>58</v>
       </c>
       <c r="Q54" s="2" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="V54" s="2" t="inlineStr"/>
     </row>
-    <row r="55" ht="107" customHeight="1">
+    <row r="55" ht="88" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5275,7 +5275,7 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr"/>
@@ -5303,7 +5303,7 @@
       <c r="J55" s="4" t="inlineStr"/>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#059；位置：L030-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#059；位置：L030-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -5328,7 +5328,7 @@
         <v>59</v>
       </c>
       <c r="Q55" s="4" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="R55" s="4" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="S55" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T55" s="4" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="V55" s="4" t="inlineStr"/>
     </row>
-    <row r="56" ht="107" customHeight="1">
+    <row r="56" ht="88" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -5378,7 +5378,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr"/>
@@ -5391,7 +5391,7 @@
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#060；位置：L030-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#060；位置：L030-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -5416,7 +5416,7 @@
         <v>60</v>
       </c>
       <c r="Q56" s="2" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="V56" s="2" t="inlineStr"/>
     </row>
-    <row r="57" ht="107" customHeight="1">
+    <row r="57" ht="88" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr"/>
@@ -5479,7 +5479,7 @@
       <c r="J57" s="4" t="inlineStr"/>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#061；位置：L031-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#061；位置：L031-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -5504,7 +5504,7 @@
         <v>61</v>
       </c>
       <c r="Q57" s="4" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="R57" s="4" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="S57" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T57" s="4" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="V57" s="4" t="inlineStr"/>
     </row>
-    <row r="58" ht="107" customHeight="1">
+    <row r="58" ht="88" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
@@ -5567,7 +5567,7 @@
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#062；位置：L031-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#062；位置：L031-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -5592,7 +5592,7 @@
         <v>62</v>
       </c>
       <c r="Q58" s="2" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="V58" s="2" t="inlineStr"/>
     </row>
-    <row r="59" ht="107" customHeight="1">
+    <row r="59" ht="88" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr"/>
@@ -5655,7 +5655,7 @@
       <c r="J59" s="4" t="inlineStr"/>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#063；位置：L032-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#063；位置：L032-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -5680,7 +5680,7 @@
         <v>63</v>
       </c>
       <c r="Q59" s="4" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="R59" s="4" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="S59" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T59" s="4" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="V59" s="4" t="inlineStr"/>
     </row>
-    <row r="60" ht="107" customHeight="1">
+    <row r="60" ht="88" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>304H</t>
+          <t>SA-213TP304H</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr"/>
@@ -5743,7 +5743,7 @@
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R38#064；位置：L032-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格/牌号按本源行保留；材质304H与区带映射一致，Φ54×7.5与其他行配对(304H↔Φ51×8)不一致，需材料专业确认</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#064；位置：L032-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -5768,7 +5768,7 @@
         <v>64</v>
       </c>
       <c r="Q60" s="2" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="V60" s="2" t="inlineStr"/>
     </row>
-    <row r="61" ht="88" customHeight="1">
+    <row r="61" ht="107" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr"/>
@@ -5831,7 +5831,7 @@
       <c r="J61" s="4" t="inlineStr"/>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#001；位置：L001-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#001；位置：L001-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -5856,7 +5856,7 @@
         <v>1</v>
       </c>
       <c r="Q61" s="4" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="R61" s="4" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
       </c>
       <c r="S61" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T61" s="4" t="inlineStr">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="V61" s="4" t="inlineStr"/>
     </row>
-    <row r="62" ht="88" customHeight="1">
+    <row r="62" ht="107" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
@@ -5919,7 +5919,7 @@
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#002；位置：L002-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#002；位置：L002-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -5944,7 +5944,7 @@
         <v>2</v>
       </c>
       <c r="Q62" s="2" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V62" s="2" t="inlineStr"/>
     </row>
-    <row r="63" ht="88" customHeight="1">
+    <row r="63" ht="107" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -5994,7 +5994,7 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr"/>
@@ -6007,7 +6007,7 @@
       <c r="J63" s="4" t="inlineStr"/>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#003；位置：L003-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#003；位置：L003-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -6032,7 +6032,7 @@
         <v>3</v>
       </c>
       <c r="Q63" s="4" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="R63" s="4" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
       </c>
       <c r="S63" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T63" s="4" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="V63" s="4" t="inlineStr"/>
     </row>
-    <row r="64" ht="88" customHeight="1">
+    <row r="64" ht="107" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6067,7 +6067,7 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr"/>
@@ -6095,7 +6095,7 @@
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#004；位置：L004-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#004；位置：L004-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
@@ -6120,7 +6120,7 @@
         <v>4</v>
       </c>
       <c r="Q64" s="2" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="V64" s="2" t="inlineStr"/>
     </row>
-    <row r="65" ht="88" customHeight="1">
+    <row r="65" ht="107" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6155,7 +6155,7 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr"/>
@@ -6183,7 +6183,7 @@
       <c r="J65" s="4" t="inlineStr"/>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#005；位置：L005-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#005；位置：L005-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -6208,7 +6208,7 @@
         <v>5</v>
       </c>
       <c r="Q65" s="4" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="R65" s="4" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
       </c>
       <c r="S65" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T65" s="4" t="inlineStr">
@@ -6232,7 +6232,7 @@
       </c>
       <c r="V65" s="4" t="inlineStr"/>
     </row>
-    <row r="66" ht="88" customHeight="1">
+    <row r="66" ht="107" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6243,7 +6243,7 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr"/>
@@ -6271,7 +6271,7 @@
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#006；位置：L006-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#006；位置：L006-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
         <v>6</v>
       </c>
       <c r="Q66" s="2" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="V66" s="2" t="inlineStr"/>
     </row>
-    <row r="67" ht="88" customHeight="1">
+    <row r="67" ht="107" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6331,7 +6331,7 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr"/>
@@ -6359,7 +6359,7 @@
       <c r="J67" s="4" t="inlineStr"/>
       <c r="K67" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#007；位置：L007-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#007；位置：L007-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -6384,7 +6384,7 @@
         <v>7</v>
       </c>
       <c r="Q67" s="4" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="R67" s="4" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="S67" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T67" s="4" t="inlineStr">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="V67" s="4" t="inlineStr"/>
     </row>
-    <row r="68" ht="88" customHeight="1">
+    <row r="68" ht="107" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr"/>
@@ -6447,7 +6447,7 @@
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#008；位置：L008-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#008；位置：L008-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
@@ -6472,7 +6472,7 @@
         <v>8</v>
       </c>
       <c r="Q68" s="2" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="V68" s="2" t="inlineStr"/>
     </row>
-    <row r="69" ht="88" customHeight="1">
+    <row r="69" ht="107" customHeight="1">
       <c r="A69" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6507,7 +6507,7 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr"/>
@@ -6535,7 +6535,7 @@
       <c r="J69" s="4" t="inlineStr"/>
       <c r="K69" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#009；位置：L009-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#009；位置：L009-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -6560,7 +6560,7 @@
         <v>9</v>
       </c>
       <c r="Q69" s="4" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="R69" s="4" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="S69" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T69" s="4" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="V69" s="4" t="inlineStr"/>
     </row>
-    <row r="70" ht="88" customHeight="1">
+    <row r="70" ht="107" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr"/>
@@ -6623,7 +6623,7 @@
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#010；位置：L010-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#010；位置：L010-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -6648,7 +6648,7 @@
         <v>10</v>
       </c>
       <c r="Q70" s="2" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="V70" s="2" t="inlineStr"/>
     </row>
-    <row r="71" ht="88" customHeight="1">
+    <row r="71" ht="107" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6683,7 +6683,7 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr"/>
@@ -6711,7 +6711,7 @@
       <c r="J71" s="4" t="inlineStr"/>
       <c r="K71" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#011；位置：L011-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#011；位置：L011-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -6736,7 +6736,7 @@
         <v>11</v>
       </c>
       <c r="Q71" s="4" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="R71" s="4" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
       </c>
       <c r="S71" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T71" s="4" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="V71" s="4" t="inlineStr"/>
     </row>
-    <row r="72" ht="88" customHeight="1">
+    <row r="72" ht="107" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr"/>
@@ -6799,7 +6799,7 @@
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#012；位置：L012-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#012；位置：L012-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
@@ -6824,7 +6824,7 @@
         <v>12</v>
       </c>
       <c r="Q72" s="2" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="V72" s="2" t="inlineStr"/>
     </row>
-    <row r="73" ht="88" customHeight="1">
+    <row r="73" ht="107" customHeight="1">
       <c r="A73" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6859,7 +6859,7 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr"/>
@@ -6887,7 +6887,7 @@
       <c r="J73" s="4" t="inlineStr"/>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#013；位置：L013-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#013；位置：L013-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
@@ -6912,7 +6912,7 @@
         <v>13</v>
       </c>
       <c r="Q73" s="4" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="R73" s="4" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
       </c>
       <c r="S73" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T73" s="4" t="inlineStr">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="V73" s="4" t="inlineStr"/>
     </row>
-    <row r="74" ht="88" customHeight="1">
+    <row r="74" ht="107" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6947,7 +6947,7 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr"/>
@@ -6975,7 +6975,7 @@
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#014；位置：L014-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#014；位置：L014-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -7000,7 +7000,7 @@
         <v>14</v>
       </c>
       <c r="Q74" s="2" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
@@ -7024,7 +7024,7 @@
       </c>
       <c r="V74" s="2" t="inlineStr"/>
     </row>
-    <row r="75" ht="88" customHeight="1">
+    <row r="75" ht="107" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7035,7 +7035,7 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr"/>
@@ -7063,7 +7063,7 @@
       <c r="J75" s="4" t="inlineStr"/>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#015；位置：L015-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#015；位置：L015-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
@@ -7088,7 +7088,7 @@
         <v>15</v>
       </c>
       <c r="Q75" s="4" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="R75" s="4" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="S75" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T75" s="4" t="inlineStr">
@@ -7112,7 +7112,7 @@
       </c>
       <c r="V75" s="4" t="inlineStr"/>
     </row>
-    <row r="76" ht="88" customHeight="1">
+    <row r="76" ht="107" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7123,7 +7123,7 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -7138,7 +7138,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr"/>
@@ -7151,7 +7151,7 @@
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#016；位置：L016-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#016；位置：L016-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -7176,7 +7176,7 @@
         <v>16</v>
       </c>
       <c r="Q76" s="2" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R76" s="2" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="V76" s="2" t="inlineStr"/>
     </row>
-    <row r="77" ht="88" customHeight="1">
+    <row r="77" ht="107" customHeight="1">
       <c r="A77" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7211,7 +7211,7 @@
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -7226,7 +7226,7 @@
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr"/>
@@ -7239,7 +7239,7 @@
       <c r="J77" s="4" t="inlineStr"/>
       <c r="K77" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#017；位置：L017-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#017；位置：L017-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
@@ -7264,7 +7264,7 @@
         <v>17</v>
       </c>
       <c r="Q77" s="4" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="R77" s="4" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
       </c>
       <c r="S77" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T77" s="4" t="inlineStr">
@@ -7288,7 +7288,7 @@
       </c>
       <c r="V77" s="4" t="inlineStr"/>
     </row>
-    <row r="78" ht="88" customHeight="1">
+    <row r="78" ht="107" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7299,7 +7299,7 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr"/>
@@ -7327,7 +7327,7 @@
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#018；位置：L018-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#018；位置：L018-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -7352,7 +7352,7 @@
         <v>18</v>
       </c>
       <c r="Q78" s="2" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="R78" s="2" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T78" s="2" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="V78" s="2" t="inlineStr"/>
     </row>
-    <row r="79" ht="88" customHeight="1">
+    <row r="79" ht="107" customHeight="1">
       <c r="A79" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7387,7 +7387,7 @@
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -7402,7 +7402,7 @@
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr"/>
@@ -7415,7 +7415,7 @@
       <c r="J79" s="4" t="inlineStr"/>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#019；位置：L019-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#019；位置：L019-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
@@ -7440,7 +7440,7 @@
         <v>19</v>
       </c>
       <c r="Q79" s="4" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="R79" s="4" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
       </c>
       <c r="S79" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T79" s="4" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="V79" s="4" t="inlineStr"/>
     </row>
-    <row r="80" ht="88" customHeight="1">
+    <row r="80" ht="107" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr"/>
@@ -7503,7 +7503,7 @@
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#020；位置：L020-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#020；位置：L020-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
@@ -7528,7 +7528,7 @@
         <v>20</v>
       </c>
       <c r="Q80" s="2" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="R80" s="2" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
@@ -7552,7 +7552,7 @@
       </c>
       <c r="V80" s="2" t="inlineStr"/>
     </row>
-    <row r="81" ht="88" customHeight="1">
+    <row r="81" ht="107" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr"/>
@@ -7591,7 +7591,7 @@
       <c r="J81" s="4" t="inlineStr"/>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#021；位置：L021-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#021；位置：L021-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
@@ -7616,7 +7616,7 @@
         <v>21</v>
       </c>
       <c r="Q81" s="4" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="R81" s="4" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
       </c>
       <c r="S81" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T81" s="4" t="inlineStr">
@@ -7640,7 +7640,7 @@
       </c>
       <c r="V81" s="4" t="inlineStr"/>
     </row>
-    <row r="82" ht="88" customHeight="1">
+    <row r="82" ht="107" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7651,7 +7651,7 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr"/>
@@ -7679,7 +7679,7 @@
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#022；位置：L022-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#022；位置：L022-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -7704,7 +7704,7 @@
         <v>22</v>
       </c>
       <c r="Q82" s="2" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="R82" s="2" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="V82" s="2" t="inlineStr"/>
     </row>
-    <row r="83" ht="88" customHeight="1">
+    <row r="83" ht="107" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7739,7 +7739,7 @@
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -7754,7 +7754,7 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr"/>
@@ -7767,7 +7767,7 @@
       <c r="J83" s="4" t="inlineStr"/>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#023；位置：L023-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#023；位置：L023-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
@@ -7792,7 +7792,7 @@
         <v>23</v>
       </c>
       <c r="Q83" s="4" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="R83" s="4" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="S83" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T83" s="4" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="V83" s="4" t="inlineStr"/>
     </row>
-    <row r="84" ht="88" customHeight="1">
+    <row r="84" ht="107" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr"/>
@@ -7855,7 +7855,7 @@
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#024；位置：L024-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#024；位置：L024-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
@@ -7880,7 +7880,7 @@
         <v>24</v>
       </c>
       <c r="Q84" s="2" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="R84" s="2" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T84" s="2" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="V84" s="2" t="inlineStr"/>
     </row>
-    <row r="85" ht="88" customHeight="1">
+    <row r="85" ht="107" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7915,7 +7915,7 @@
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr"/>
@@ -7943,7 +7943,7 @@
       <c r="J85" s="4" t="inlineStr"/>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#025；位置：L025-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#025；位置：L025-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
@@ -7968,7 +7968,7 @@
         <v>25</v>
       </c>
       <c r="Q85" s="4" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="R85" s="4" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
       </c>
       <c r="S85" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T85" s="4" t="inlineStr">
@@ -7992,7 +7992,7 @@
       </c>
       <c r="V85" s="4" t="inlineStr"/>
     </row>
-    <row r="86" ht="88" customHeight="1">
+    <row r="86" ht="107" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -8018,7 +8018,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr"/>
@@ -8031,7 +8031,7 @@
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#026；位置：L026-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#026；位置：L026-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
@@ -8056,7 +8056,7 @@
         <v>26</v>
       </c>
       <c r="Q86" s="2" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="R86" s="2" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="V86" s="2" t="inlineStr"/>
     </row>
-    <row r="87" ht="88" customHeight="1">
+    <row r="87" ht="107" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr"/>
@@ -8119,7 +8119,7 @@
       <c r="J87" s="4" t="inlineStr"/>
       <c r="K87" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#027；位置：L027-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#027；位置：L027-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
@@ -8144,7 +8144,7 @@
         <v>27</v>
       </c>
       <c r="Q87" s="4" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="R87" s="4" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="S87" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T87" s="4" t="inlineStr">
@@ -8168,7 +8168,7 @@
       </c>
       <c r="V87" s="4" t="inlineStr"/>
     </row>
-    <row r="88" ht="88" customHeight="1">
+    <row r="88" ht="107" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr"/>
@@ -8207,7 +8207,7 @@
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#028；位置：L028-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#028；位置：L028-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
@@ -8232,7 +8232,7 @@
         <v>28</v>
       </c>
       <c r="Q88" s="2" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="R88" s="2" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T88" s="2" t="inlineStr">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="V88" s="2" t="inlineStr"/>
     </row>
-    <row r="89" ht="88" customHeight="1">
+    <row r="89" ht="107" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8267,7 +8267,7 @@
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr"/>
@@ -8295,7 +8295,7 @@
       <c r="J89" s="4" t="inlineStr"/>
       <c r="K89" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#029；位置：L029-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#029；位置：L029-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
@@ -8320,7 +8320,7 @@
         <v>29</v>
       </c>
       <c r="Q89" s="4" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="R89" s="4" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
       </c>
       <c r="S89" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T89" s="4" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="V89" s="4" t="inlineStr"/>
     </row>
-    <row r="90" ht="88" customHeight="1">
+    <row r="90" ht="107" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8355,7 +8355,7 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr"/>
@@ -8383,7 +8383,7 @@
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#030；位置：L030-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#030；位置：L030-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -8408,7 +8408,7 @@
         <v>30</v>
       </c>
       <c r="Q90" s="2" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="R90" s="2" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T90" s="2" t="inlineStr">
@@ -8432,7 +8432,7 @@
       </c>
       <c r="V90" s="2" t="inlineStr"/>
     </row>
-    <row r="91" ht="88" customHeight="1">
+    <row r="91" ht="107" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8443,7 +8443,7 @@
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr"/>
@@ -8471,7 +8471,7 @@
       <c r="J91" s="4" t="inlineStr"/>
       <c r="K91" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#031；位置：L031-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#031；位置：L031-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L91" s="4" t="inlineStr">
@@ -8496,7 +8496,7 @@
         <v>31</v>
       </c>
       <c r="Q91" s="4" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="R91" s="4" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
       </c>
       <c r="S91" s="4" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T91" s="4" t="inlineStr">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="V91" s="4" t="inlineStr"/>
     </row>
-    <row r="92" ht="88" customHeight="1">
+    <row r="92" ht="107" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8531,7 +8531,7 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>TP347H</t>
+          <t>SA-213TP347H</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr"/>
@@ -8559,7 +8559,7 @@
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=年，月日未提供；来源ID：2026年1号机C修!R39#032；位置：L032-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#032；位置：L032-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
@@ -8584,7 +8584,7 @@
         <v>32</v>
       </c>
       <c r="Q92" s="2" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="R92" s="2" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
       </c>
       <c r="S92" s="2" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>月</t>
         </is>
       </c>
       <c r="T92" s="2" t="inlineStr">

--- a/data-cleaning/verified/增量_2026年1号机C修_汇总展开91.xlsx
+++ b/data-cleaning/verified/增量_2026年1号机C修_汇总展开91.xlsx
@@ -600,7 +600,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="88" customHeight="1">
+    <row r="2" ht="107" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -621,7 +621,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#001；位置：L001-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#001；位置：L001-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="V2" s="2" t="inlineStr"/>
     </row>
-    <row r="3" ht="88" customHeight="1">
+    <row r="3" ht="107" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -709,7 +709,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -727,7 +727,7 @@
       <c r="J3" s="4" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#002；位置：L001-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#002；位置：L001-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="V3" s="4" t="inlineStr"/>
     </row>
-    <row r="4" ht="88" customHeight="1">
+    <row r="4" ht="107" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -797,7 +797,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#003；位置：L002-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#003；位置：L002-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr"/>
     </row>
-    <row r="5" ht="88" customHeight="1">
+    <row r="5" ht="107" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -885,7 +885,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -903,7 +903,7 @@
       <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#004；位置：L002-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#004；位置：L002-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="V5" s="4" t="inlineStr"/>
     </row>
-    <row r="6" ht="88" customHeight="1">
+    <row r="6" ht="107" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -973,7 +973,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#005；位置：L003-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#005；位置：L003-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr"/>
     </row>
-    <row r="7" ht="88" customHeight="1">
+    <row r="7" ht="107" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -1079,7 +1079,7 @@
       <c r="J7" s="4" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#006；位置：L003-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#006；位置：L003-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="V7" s="4" t="inlineStr"/>
     </row>
-    <row r="8" ht="88" customHeight="1">
+    <row r="8" ht="107" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1167,7 +1167,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#007；位置：L004-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#007；位置：L004-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr"/>
     </row>
-    <row r="9" ht="88" customHeight="1">
+    <row r="9" ht="107" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1255,7 +1255,7 @@
       <c r="J9" s="4" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#010；位置：L005-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#010；位置：L005-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="V9" s="4" t="inlineStr"/>
     </row>
-    <row r="10" ht="88" customHeight="1">
+    <row r="10" ht="107" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1343,7 +1343,7 @@
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#011；位置：L006-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#011；位置：L006-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr"/>
     </row>
-    <row r="11" ht="88" customHeight="1">
+    <row r="11" ht="107" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1431,7 +1431,7 @@
       <c r="J11" s="4" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#012；位置：L006-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#012；位置：L006-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="V11" s="4" t="inlineStr"/>
     </row>
-    <row r="12" ht="88" customHeight="1">
+    <row r="12" ht="107" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1519,7 +1519,7 @@
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#013；位置：L007-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#013；位置：L007-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr"/>
     </row>
-    <row r="13" ht="88" customHeight="1">
+    <row r="13" ht="107" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1607,7 +1607,7 @@
       <c r="J13" s="4" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#014；位置：L007-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#014；位置：L007-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="V13" s="4" t="inlineStr"/>
     </row>
-    <row r="14" ht="88" customHeight="1">
+    <row r="14" ht="107" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#015；位置：L008-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#015；位置：L008-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr"/>
     </row>
-    <row r="15" ht="88" customHeight="1">
+    <row r="15" ht="107" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1783,7 +1783,7 @@
       <c r="J15" s="4" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#016；位置：L008-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#016；位置：L008-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="V15" s="4" t="inlineStr"/>
     </row>
-    <row r="16" ht="88" customHeight="1">
+    <row r="16" ht="107" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1871,7 +1871,7 @@
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#017；位置：L009-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#017；位置：L009-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr"/>
     </row>
-    <row r="17" ht="88" customHeight="1">
+    <row r="17" ht="107" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -1959,7 +1959,7 @@
       <c r="J17" s="4" t="inlineStr"/>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#018；位置：L009-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#018；位置：L009-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="V17" s="4" t="inlineStr"/>
     </row>
-    <row r="18" ht="88" customHeight="1">
+    <row r="18" ht="107" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2047,7 +2047,7 @@
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#020；位置：L010-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#020；位置：L010-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr"/>
     </row>
-    <row r="19" ht="88" customHeight="1">
+    <row r="19" ht="107" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -2135,7 +2135,7 @@
       <c r="J19" s="4" t="inlineStr"/>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#021；位置：L011-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#021；位置：L011-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="V19" s="4" t="inlineStr"/>
     </row>
-    <row r="20" ht="88" customHeight="1">
+    <row r="20" ht="107" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#022；位置：L011-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#022；位置：L011-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr"/>
     </row>
-    <row r="21" ht="88" customHeight="1">
+    <row r="21" ht="107" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -2311,7 +2311,7 @@
       <c r="J21" s="4" t="inlineStr"/>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#023；位置：L012-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#023；位置：L012-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="V21" s="4" t="inlineStr"/>
     </row>
-    <row r="22" ht="88" customHeight="1">
+    <row r="22" ht="107" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2399,7 +2399,7 @@
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#024；位置：L012-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#024；位置：L012-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr"/>
     </row>
-    <row r="23" ht="88" customHeight="1">
+    <row r="23" ht="107" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -2487,7 +2487,7 @@
       <c r="J23" s="4" t="inlineStr"/>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#026；位置：L013-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#026；位置：L013-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="V23" s="4" t="inlineStr"/>
     </row>
-    <row r="24" ht="88" customHeight="1">
+    <row r="24" ht="107" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#027；位置：L014-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#027；位置：L014-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr"/>
     </row>
-    <row r="25" ht="88" customHeight="1">
+    <row r="25" ht="107" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -2663,7 +2663,7 @@
       <c r="J25" s="4" t="inlineStr"/>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#028；位置：L014-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#028；位置：L014-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="V25" s="4" t="inlineStr"/>
     </row>
-    <row r="26" ht="88" customHeight="1">
+    <row r="26" ht="107" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2751,7 +2751,7 @@
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#029；位置：L015-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#029；位置：L015-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr"/>
     </row>
-    <row r="27" ht="88" customHeight="1">
+    <row r="27" ht="107" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -2839,7 +2839,7 @@
       <c r="J27" s="4" t="inlineStr"/>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#030；位置：L015-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#030；位置：L015-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="V27" s="4" t="inlineStr"/>
     </row>
-    <row r="28" ht="88" customHeight="1">
+    <row r="28" ht="107" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -2927,7 +2927,7 @@
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#031；位置：L016-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#031；位置：L016-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr"/>
     </row>
-    <row r="29" ht="88" customHeight="1">
+    <row r="29" ht="107" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -3015,7 +3015,7 @@
       <c r="J29" s="4" t="inlineStr"/>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#032；位置：L016-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#032；位置：L016-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="V29" s="4" t="inlineStr"/>
     </row>
-    <row r="30" ht="88" customHeight="1">
+    <row r="30" ht="107" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#033；位置：L017-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#033；位置：L017-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr"/>
     </row>
-    <row r="31" ht="88" customHeight="1">
+    <row r="31" ht="107" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -3191,7 +3191,7 @@
       <c r="J31" s="4" t="inlineStr"/>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#034；位置：L017-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#034；位置：L017-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="V31" s="4" t="inlineStr"/>
     </row>
-    <row r="32" ht="88" customHeight="1">
+    <row r="32" ht="107" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#035；位置：L018-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#035；位置：L018-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr"/>
     </row>
-    <row r="33" ht="88" customHeight="1">
+    <row r="33" ht="107" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -3367,7 +3367,7 @@
       <c r="J33" s="4" t="inlineStr"/>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#036；位置：L018-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#036；位置：L018-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="V33" s="4" t="inlineStr"/>
     </row>
-    <row r="34" ht="88" customHeight="1">
+    <row r="34" ht="107" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3437,7 +3437,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#037；位置：L019-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#037；位置：L019-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr"/>
     </row>
-    <row r="35" ht="88" customHeight="1">
+    <row r="35" ht="107" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -3543,7 +3543,7 @@
       <c r="J35" s="4" t="inlineStr"/>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#038；位置：L019-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#038；位置：L019-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="V35" s="4" t="inlineStr"/>
     </row>
-    <row r="36" ht="88" customHeight="1">
+    <row r="36" ht="107" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3613,7 +3613,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -3631,7 +3631,7 @@
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#039；位置：L020-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#039；位置：L020-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr"/>
     </row>
-    <row r="37" ht="88" customHeight="1">
+    <row r="37" ht="107" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -3719,7 +3719,7 @@
       <c r="J37" s="4" t="inlineStr"/>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#040；位置：L020-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#040；位置：L020-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="V37" s="4" t="inlineStr"/>
     </row>
-    <row r="38" ht="88" customHeight="1">
+    <row r="38" ht="107" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -3807,7 +3807,7 @@
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#041；位置：L021-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#041；位置：L021-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="V38" s="2" t="inlineStr"/>
     </row>
-    <row r="39" ht="88" customHeight="1">
+    <row r="39" ht="107" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -3895,7 +3895,7 @@
       <c r="J39" s="4" t="inlineStr"/>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#042；位置：L021-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#042；位置：L021-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="V39" s="4" t="inlineStr"/>
     </row>
-    <row r="40" ht="88" customHeight="1">
+    <row r="40" ht="107" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -3983,7 +3983,7 @@
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#043；位置：L022-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#043；位置：L022-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="V40" s="2" t="inlineStr"/>
     </row>
-    <row r="41" ht="88" customHeight="1">
+    <row r="41" ht="107" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4053,7 +4053,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -4071,7 +4071,7 @@
       <c r="J41" s="4" t="inlineStr"/>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#044；位置：L022-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#044；位置：L022-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="V41" s="4" t="inlineStr"/>
     </row>
-    <row r="42" ht="88" customHeight="1">
+    <row r="42" ht="107" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -4159,7 +4159,7 @@
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#045；位置：L023-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#045；位置：L023-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="V42" s="2" t="inlineStr"/>
     </row>
-    <row r="43" ht="88" customHeight="1">
+    <row r="43" ht="107" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -4247,7 +4247,7 @@
       <c r="J43" s="4" t="inlineStr"/>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#046；位置：L023-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#046；位置：L023-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="V43" s="4" t="inlineStr"/>
     </row>
-    <row r="44" ht="88" customHeight="1">
+    <row r="44" ht="107" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -4335,7 +4335,7 @@
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#047；位置：L024-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#047；位置：L024-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="V44" s="2" t="inlineStr"/>
     </row>
-    <row r="45" ht="88" customHeight="1">
+    <row r="45" ht="107" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -4423,7 +4423,7 @@
       <c r="J45" s="4" t="inlineStr"/>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#048；位置：L024-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#048；位置：L024-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="V45" s="4" t="inlineStr"/>
     </row>
-    <row r="46" ht="88" customHeight="1">
+    <row r="46" ht="107" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4493,7 +4493,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -4511,7 +4511,7 @@
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#050；位置：L025-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#050；位置：L025-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="V46" s="2" t="inlineStr"/>
     </row>
-    <row r="47" ht="88" customHeight="1">
+    <row r="47" ht="107" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -4599,7 +4599,7 @@
       <c r="J47" s="4" t="inlineStr"/>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#051；位置：L026-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#051；位置：L026-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="V47" s="4" t="inlineStr"/>
     </row>
-    <row r="48" ht="88" customHeight="1">
+    <row r="48" ht="107" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -4687,7 +4687,7 @@
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#052；位置：L026-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#052；位置：L026-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="V48" s="2" t="inlineStr"/>
     </row>
-    <row r="49" ht="88" customHeight="1">
+    <row r="49" ht="107" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -4775,7 +4775,7 @@
       <c r="J49" s="4" t="inlineStr"/>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#053；位置：L027-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#053；位置：L027-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V49" s="4" t="inlineStr"/>
     </row>
-    <row r="50" ht="88" customHeight="1">
+    <row r="50" ht="107" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -4863,7 +4863,7 @@
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#054；位置：L027-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#054；位置：L027-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="V50" s="2" t="inlineStr"/>
     </row>
-    <row r="51" ht="88" customHeight="1">
+    <row r="51" ht="107" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -4951,7 +4951,7 @@
       <c r="J51" s="4" t="inlineStr"/>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#055；位置：L028-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#055；位置：L028-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="V51" s="4" t="inlineStr"/>
     </row>
-    <row r="52" ht="88" customHeight="1">
+    <row r="52" ht="107" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5021,7 +5021,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -5039,7 +5039,7 @@
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#056；位置：L028-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#056；位置：L028-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="V52" s="2" t="inlineStr"/>
     </row>
-    <row r="53" ht="88" customHeight="1">
+    <row r="53" ht="107" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -5127,7 +5127,7 @@
       <c r="J53" s="4" t="inlineStr"/>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#057；位置：L029-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#057；位置：L029-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="V53" s="4" t="inlineStr"/>
     </row>
-    <row r="54" ht="88" customHeight="1">
+    <row r="54" ht="107" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -5215,7 +5215,7 @@
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#058；位置：L029-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#058；位置：L029-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="V54" s="2" t="inlineStr"/>
     </row>
-    <row r="55" ht="88" customHeight="1">
+    <row r="55" ht="107" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5285,7 +5285,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -5303,7 +5303,7 @@
       <c r="J55" s="4" t="inlineStr"/>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#059；位置：L030-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#059；位置：L030-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="V55" s="4" t="inlineStr"/>
     </row>
-    <row r="56" ht="88" customHeight="1">
+    <row r="56" ht="107" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -5391,7 +5391,7 @@
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#060；位置：L030-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#060；位置：L030-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="V56" s="2" t="inlineStr"/>
     </row>
-    <row r="57" ht="88" customHeight="1">
+    <row r="57" ht="107" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -5479,7 +5479,7 @@
       <c r="J57" s="4" t="inlineStr"/>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#061；位置：L031-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#061；位置：L031-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="V57" s="4" t="inlineStr"/>
     </row>
-    <row r="58" ht="88" customHeight="1">
+    <row r="58" ht="107" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5549,7 +5549,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#062；位置：L031-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#062；位置：L031-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="V58" s="2" t="inlineStr"/>
     </row>
-    <row r="59" ht="88" customHeight="1">
+    <row r="59" ht="107" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5637,7 +5637,7 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -5655,7 +5655,7 @@
       <c r="J59" s="4" t="inlineStr"/>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#063；位置：L032-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#063；位置：L032-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="V59" s="4" t="inlineStr"/>
     </row>
-    <row r="60" ht="88" customHeight="1">
+    <row r="60" ht="107" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Φ54×7.5</t>
+          <t>Φ51×8</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -5743,7 +5743,7 @@
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#064；位置：L032-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格</t>
+          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#064；位置：L032-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">

--- a/data-cleaning/verified/增量_2026年1号机C修_汇总展开91.xlsx
+++ b/data-cleaning/verified/增量_2026年1号机C修_汇总展开91.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="107" customHeight="1">
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -600,7 +600,7 @@
       <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#001；位置：L001-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="V2" s="1" t="inlineStr"/>
     </row>
-    <row r="3" ht="107" customHeight="1">
+    <row r="3" ht="32" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -688,7 +688,7 @@
       <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#002；位置：L001-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="V3" s="1" t="inlineStr"/>
     </row>
-    <row r="4" ht="107" customHeight="1">
+    <row r="4" ht="32" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -776,7 +776,7 @@
       <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#003；位置：L002-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="V4" s="1" t="inlineStr"/>
     </row>
-    <row r="5" ht="107" customHeight="1">
+    <row r="5" ht="32" customHeight="1">
       <c r="A5" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -864,7 +864,7 @@
       <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#004；位置：L002-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="V5" s="1" t="inlineStr"/>
     </row>
-    <row r="6" ht="107" customHeight="1">
+    <row r="6" ht="32" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -952,7 +952,7 @@
       <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#005；位置：L003-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="V6" s="1" t="inlineStr"/>
     </row>
-    <row r="7" ht="107" customHeight="1">
+    <row r="7" ht="32" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1040,7 +1040,7 @@
       <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#006；位置：L003-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="V7" s="1" t="inlineStr"/>
     </row>
-    <row r="8" ht="107" customHeight="1">
+    <row r="8" ht="32" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1128,7 +1128,7 @@
       <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#007；位置：L004-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="V8" s="1" t="inlineStr"/>
     </row>
-    <row r="9" ht="107" customHeight="1">
+    <row r="9" ht="32" customHeight="1">
       <c r="A9" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1216,7 +1216,7 @@
       <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#010；位置：L005-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="V9" s="1" t="inlineStr"/>
     </row>
-    <row r="10" ht="107" customHeight="1">
+    <row r="10" ht="32" customHeight="1">
       <c r="A10" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1304,7 +1304,7 @@
       <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#011；位置：L006-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="V10" s="1" t="inlineStr"/>
     </row>
-    <row r="11" ht="107" customHeight="1">
+    <row r="11" ht="32" customHeight="1">
       <c r="A11" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1392,7 +1392,7 @@
       <c r="J11" s="1" t="inlineStr"/>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#012；位置：L006-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="V11" s="1" t="inlineStr"/>
     </row>
-    <row r="12" ht="107" customHeight="1">
+    <row r="12" ht="32" customHeight="1">
       <c r="A12" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1480,7 +1480,7 @@
       <c r="J12" s="1" t="inlineStr"/>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#013；位置：L007-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="V12" s="1" t="inlineStr"/>
     </row>
-    <row r="13" ht="107" customHeight="1">
+    <row r="13" ht="32" customHeight="1">
       <c r="A13" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1568,7 +1568,7 @@
       <c r="J13" s="1" t="inlineStr"/>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#014；位置：L007-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V13" s="1" t="inlineStr"/>
     </row>
-    <row r="14" ht="107" customHeight="1">
+    <row r="14" ht="32" customHeight="1">
       <c r="A14" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1656,7 +1656,7 @@
       <c r="J14" s="1" t="inlineStr"/>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#015；位置：L008-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="V14" s="1" t="inlineStr"/>
     </row>
-    <row r="15" ht="107" customHeight="1">
+    <row r="15" ht="32" customHeight="1">
       <c r="A15" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1744,7 +1744,7 @@
       <c r="J15" s="1" t="inlineStr"/>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#016；位置：L008-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L15" s="1" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="V15" s="1" t="inlineStr"/>
     </row>
-    <row r="16" ht="107" customHeight="1">
+    <row r="16" ht="32" customHeight="1">
       <c r="A16" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1832,7 +1832,7 @@
       <c r="J16" s="1" t="inlineStr"/>
       <c r="K16" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#017；位置：L009-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L16" s="1" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="V16" s="1" t="inlineStr"/>
     </row>
-    <row r="17" ht="107" customHeight="1">
+    <row r="17" ht="32" customHeight="1">
       <c r="A17" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -1920,7 +1920,7 @@
       <c r="J17" s="1" t="inlineStr"/>
       <c r="K17" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#018；位置：L009-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L17" s="1" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="V17" s="1" t="inlineStr"/>
     </row>
-    <row r="18" ht="107" customHeight="1">
+    <row r="18" ht="32" customHeight="1">
       <c r="A18" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2008,7 +2008,7 @@
       <c r="J18" s="1" t="inlineStr"/>
       <c r="K18" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#020；位置：L010-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L18" s="1" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="V18" s="1" t="inlineStr"/>
     </row>
-    <row r="19" ht="107" customHeight="1">
+    <row r="19" ht="32" customHeight="1">
       <c r="A19" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2096,7 +2096,7 @@
       <c r="J19" s="1" t="inlineStr"/>
       <c r="K19" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#021；位置：L011-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L19" s="1" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="V19" s="1" t="inlineStr"/>
     </row>
-    <row r="20" ht="107" customHeight="1">
+    <row r="20" ht="32" customHeight="1">
       <c r="A20" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2184,7 +2184,7 @@
       <c r="J20" s="1" t="inlineStr"/>
       <c r="K20" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#022；位置：L011-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L20" s="1" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="V20" s="1" t="inlineStr"/>
     </row>
-    <row r="21" ht="107" customHeight="1">
+    <row r="21" ht="32" customHeight="1">
       <c r="A21" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2272,7 +2272,7 @@
       <c r="J21" s="1" t="inlineStr"/>
       <c r="K21" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#023；位置：L012-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L21" s="1" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="V21" s="1" t="inlineStr"/>
     </row>
-    <row r="22" ht="107" customHeight="1">
+    <row r="22" ht="32" customHeight="1">
       <c r="A22" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2360,7 +2360,7 @@
       <c r="J22" s="1" t="inlineStr"/>
       <c r="K22" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#024；位置：L012-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L22" s="1" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="V22" s="1" t="inlineStr"/>
     </row>
-    <row r="23" ht="107" customHeight="1">
+    <row r="23" ht="32" customHeight="1">
       <c r="A23" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2448,7 +2448,7 @@
       <c r="J23" s="1" t="inlineStr"/>
       <c r="K23" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#026；位置：L013-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L23" s="1" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="V23" s="1" t="inlineStr"/>
     </row>
-    <row r="24" ht="107" customHeight="1">
+    <row r="24" ht="32" customHeight="1">
       <c r="A24" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2536,7 +2536,7 @@
       <c r="J24" s="1" t="inlineStr"/>
       <c r="K24" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#027；位置：L014-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L24" s="1" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="V24" s="1" t="inlineStr"/>
     </row>
-    <row r="25" ht="107" customHeight="1">
+    <row r="25" ht="32" customHeight="1">
       <c r="A25" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2624,7 +2624,7 @@
       <c r="J25" s="1" t="inlineStr"/>
       <c r="K25" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#028；位置：L014-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L25" s="1" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="V25" s="1" t="inlineStr"/>
     </row>
-    <row r="26" ht="107" customHeight="1">
+    <row r="26" ht="32" customHeight="1">
       <c r="A26" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2712,7 +2712,7 @@
       <c r="J26" s="1" t="inlineStr"/>
       <c r="K26" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#029；位置：L015-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L26" s="1" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="V26" s="1" t="inlineStr"/>
     </row>
-    <row r="27" ht="107" customHeight="1">
+    <row r="27" ht="32" customHeight="1">
       <c r="A27" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2800,7 +2800,7 @@
       <c r="J27" s="1" t="inlineStr"/>
       <c r="K27" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#030；位置：L015-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L27" s="1" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="V27" s="1" t="inlineStr"/>
     </row>
-    <row r="28" ht="107" customHeight="1">
+    <row r="28" ht="32" customHeight="1">
       <c r="A28" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2888,7 +2888,7 @@
       <c r="J28" s="1" t="inlineStr"/>
       <c r="K28" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#031；位置：L016-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L28" s="1" t="inlineStr">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="V28" s="1" t="inlineStr"/>
     </row>
-    <row r="29" ht="107" customHeight="1">
+    <row r="29" ht="32" customHeight="1">
       <c r="A29" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -2976,7 +2976,7 @@
       <c r="J29" s="1" t="inlineStr"/>
       <c r="K29" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#032；位置：L016-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L29" s="1" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="V29" s="1" t="inlineStr"/>
     </row>
-    <row r="30" ht="107" customHeight="1">
+    <row r="30" ht="32" customHeight="1">
       <c r="A30" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3064,7 +3064,7 @@
       <c r="J30" s="1" t="inlineStr"/>
       <c r="K30" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#033；位置：L017-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L30" s="1" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="V30" s="1" t="inlineStr"/>
     </row>
-    <row r="31" ht="107" customHeight="1">
+    <row r="31" ht="32" customHeight="1">
       <c r="A31" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3152,7 +3152,7 @@
       <c r="J31" s="1" t="inlineStr"/>
       <c r="K31" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#034；位置：L017-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L31" s="1" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="V31" s="1" t="inlineStr"/>
     </row>
-    <row r="32" ht="107" customHeight="1">
+    <row r="32" ht="32" customHeight="1">
       <c r="A32" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3240,7 +3240,7 @@
       <c r="J32" s="1" t="inlineStr"/>
       <c r="K32" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#035；位置：L018-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L32" s="1" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="V32" s="1" t="inlineStr"/>
     </row>
-    <row r="33" ht="107" customHeight="1">
+    <row r="33" ht="32" customHeight="1">
       <c r="A33" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3328,7 +3328,7 @@
       <c r="J33" s="1" t="inlineStr"/>
       <c r="K33" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#036；位置：L018-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L33" s="1" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="V33" s="1" t="inlineStr"/>
     </row>
-    <row r="34" ht="107" customHeight="1">
+    <row r="34" ht="32" customHeight="1">
       <c r="A34" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3416,7 +3416,7 @@
       <c r="J34" s="1" t="inlineStr"/>
       <c r="K34" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#037；位置：L019-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L34" s="1" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="V34" s="1" t="inlineStr"/>
     </row>
-    <row r="35" ht="107" customHeight="1">
+    <row r="35" ht="32" customHeight="1">
       <c r="A35" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3504,7 +3504,7 @@
       <c r="J35" s="1" t="inlineStr"/>
       <c r="K35" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#038；位置：L019-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L35" s="1" t="inlineStr">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="V35" s="1" t="inlineStr"/>
     </row>
-    <row r="36" ht="107" customHeight="1">
+    <row r="36" ht="32" customHeight="1">
       <c r="A36" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3592,7 +3592,7 @@
       <c r="J36" s="1" t="inlineStr"/>
       <c r="K36" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#039；位置：L020-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L36" s="1" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="V36" s="1" t="inlineStr"/>
     </row>
-    <row r="37" ht="107" customHeight="1">
+    <row r="37" ht="32" customHeight="1">
       <c r="A37" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3680,7 +3680,7 @@
       <c r="J37" s="1" t="inlineStr"/>
       <c r="K37" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#040；位置：L020-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L37" s="1" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="V37" s="1" t="inlineStr"/>
     </row>
-    <row r="38" ht="107" customHeight="1">
+    <row r="38" ht="32" customHeight="1">
       <c r="A38" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3768,7 +3768,7 @@
       <c r="J38" s="1" t="inlineStr"/>
       <c r="K38" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#041；位置：L021-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L38" s="1" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="V38" s="1" t="inlineStr"/>
     </row>
-    <row r="39" ht="107" customHeight="1">
+    <row r="39" ht="32" customHeight="1">
       <c r="A39" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3856,7 +3856,7 @@
       <c r="J39" s="1" t="inlineStr"/>
       <c r="K39" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#042；位置：L021-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L39" s="1" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="V39" s="1" t="inlineStr"/>
     </row>
-    <row r="40" ht="107" customHeight="1">
+    <row r="40" ht="32" customHeight="1">
       <c r="A40" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -3944,7 +3944,7 @@
       <c r="J40" s="1" t="inlineStr"/>
       <c r="K40" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#043；位置：L022-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L40" s="1" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="V40" s="1" t="inlineStr"/>
     </row>
-    <row r="41" ht="107" customHeight="1">
+    <row r="41" ht="32" customHeight="1">
       <c r="A41" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4032,7 +4032,7 @@
       <c r="J41" s="1" t="inlineStr"/>
       <c r="K41" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#044；位置：L022-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L41" s="1" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="V41" s="1" t="inlineStr"/>
     </row>
-    <row r="42" ht="107" customHeight="1">
+    <row r="42" ht="32" customHeight="1">
       <c r="A42" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4120,7 +4120,7 @@
       <c r="J42" s="1" t="inlineStr"/>
       <c r="K42" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#045；位置：L023-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L42" s="1" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="V42" s="1" t="inlineStr"/>
     </row>
-    <row r="43" ht="107" customHeight="1">
+    <row r="43" ht="32" customHeight="1">
       <c r="A43" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4208,7 +4208,7 @@
       <c r="J43" s="1" t="inlineStr"/>
       <c r="K43" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#046；位置：L023-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L43" s="1" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="V43" s="1" t="inlineStr"/>
     </row>
-    <row r="44" ht="107" customHeight="1">
+    <row r="44" ht="32" customHeight="1">
       <c r="A44" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4296,7 +4296,7 @@
       <c r="J44" s="1" t="inlineStr"/>
       <c r="K44" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#047；位置：L024-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L44" s="1" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="V44" s="1" t="inlineStr"/>
     </row>
-    <row r="45" ht="107" customHeight="1">
+    <row r="45" ht="32" customHeight="1">
       <c r="A45" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4384,7 +4384,7 @@
       <c r="J45" s="1" t="inlineStr"/>
       <c r="K45" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#048；位置：L024-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L45" s="1" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="V45" s="1" t="inlineStr"/>
     </row>
-    <row r="46" ht="107" customHeight="1">
+    <row r="46" ht="32" customHeight="1">
       <c r="A46" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4472,7 +4472,7 @@
       <c r="J46" s="1" t="inlineStr"/>
       <c r="K46" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#050；位置：L025-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L46" s="1" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="V46" s="1" t="inlineStr"/>
     </row>
-    <row r="47" ht="107" customHeight="1">
+    <row r="47" ht="32" customHeight="1">
       <c r="A47" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4560,7 +4560,7 @@
       <c r="J47" s="1" t="inlineStr"/>
       <c r="K47" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#051；位置：L026-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L47" s="1" t="inlineStr">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="V47" s="1" t="inlineStr"/>
     </row>
-    <row r="48" ht="107" customHeight="1">
+    <row r="48" ht="32" customHeight="1">
       <c r="A48" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4648,7 +4648,7 @@
       <c r="J48" s="1" t="inlineStr"/>
       <c r="K48" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#052；位置：L026-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L48" s="1" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="V48" s="1" t="inlineStr"/>
     </row>
-    <row r="49" ht="107" customHeight="1">
+    <row r="49" ht="32" customHeight="1">
       <c r="A49" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4736,7 +4736,7 @@
       <c r="J49" s="1" t="inlineStr"/>
       <c r="K49" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#053；位置：L027-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L49" s="1" t="inlineStr">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="V49" s="1" t="inlineStr"/>
     </row>
-    <row r="50" ht="107" customHeight="1">
+    <row r="50" ht="32" customHeight="1">
       <c r="A50" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4824,7 +4824,7 @@
       <c r="J50" s="1" t="inlineStr"/>
       <c r="K50" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#054；位置：L027-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L50" s="1" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="V50" s="1" t="inlineStr"/>
     </row>
-    <row r="51" ht="107" customHeight="1">
+    <row r="51" ht="32" customHeight="1">
       <c r="A51" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -4912,7 +4912,7 @@
       <c r="J51" s="1" t="inlineStr"/>
       <c r="K51" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#055；位置：L028-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L51" s="1" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="V51" s="1" t="inlineStr"/>
     </row>
-    <row r="52" ht="107" customHeight="1">
+    <row r="52" ht="32" customHeight="1">
       <c r="A52" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5000,7 +5000,7 @@
       <c r="J52" s="1" t="inlineStr"/>
       <c r="K52" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#056；位置：L028-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L52" s="1" t="inlineStr">
@@ -5049,7 +5049,7 @@
       </c>
       <c r="V52" s="1" t="inlineStr"/>
     </row>
-    <row r="53" ht="107" customHeight="1">
+    <row r="53" ht="32" customHeight="1">
       <c r="A53" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5088,7 +5088,7 @@
       <c r="J53" s="1" t="inlineStr"/>
       <c r="K53" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#057；位置：L029-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L53" s="1" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="V53" s="1" t="inlineStr"/>
     </row>
-    <row r="54" ht="107" customHeight="1">
+    <row r="54" ht="32" customHeight="1">
       <c r="A54" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5176,7 +5176,7 @@
       <c r="J54" s="1" t="inlineStr"/>
       <c r="K54" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#058；位置：L029-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L54" s="1" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="V54" s="1" t="inlineStr"/>
     </row>
-    <row r="55" ht="107" customHeight="1">
+    <row r="55" ht="32" customHeight="1">
       <c r="A55" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5264,7 +5264,7 @@
       <c r="J55" s="1" t="inlineStr"/>
       <c r="K55" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#059；位置：L030-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L55" s="1" t="inlineStr">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="V55" s="1" t="inlineStr"/>
     </row>
-    <row r="56" ht="107" customHeight="1">
+    <row r="56" ht="32" customHeight="1">
       <c r="A56" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5352,7 +5352,7 @@
       <c r="J56" s="1" t="inlineStr"/>
       <c r="K56" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#060；位置：L030-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L56" s="1" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="V56" s="1" t="inlineStr"/>
     </row>
-    <row r="57" ht="107" customHeight="1">
+    <row r="57" ht="32" customHeight="1">
       <c r="A57" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5440,7 +5440,7 @@
       <c r="J57" s="1" t="inlineStr"/>
       <c r="K57" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#061；位置：L031-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L57" s="1" t="inlineStr">
@@ -5489,7 +5489,7 @@
       </c>
       <c r="V57" s="1" t="inlineStr"/>
     </row>
-    <row r="58" ht="107" customHeight="1">
+    <row r="58" ht="32" customHeight="1">
       <c r="A58" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5528,7 +5528,7 @@
       <c r="J58" s="1" t="inlineStr"/>
       <c r="K58" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#062；位置：L031-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L58" s="1" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="V58" s="1" t="inlineStr"/>
     </row>
-    <row r="59" ht="107" customHeight="1">
+    <row r="59" ht="32" customHeight="1">
       <c r="A59" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5616,7 +5616,7 @@
       <c r="J59" s="1" t="inlineStr"/>
       <c r="K59" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#063；位置：L032-F002；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L59" s="1" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="V59" s="1" t="inlineStr"/>
     </row>
-    <row r="60" ht="107" customHeight="1">
+    <row r="60" ht="32" customHeight="1">
       <c r="A60" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5704,7 +5704,7 @@
       <c r="J60" s="1" t="inlineStr"/>
       <c r="K60" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R38#064；位置：L032-F003；源位置：1-32屏的炉前第2/3根共64个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；合格依据：源汇总行明确记载其余合格；规格按图纸148M211-0（高温过热器材料分界图）确认为Φ51×8；源表Φ54×7.5为笔误</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L60" s="1" t="inlineStr">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="V60" s="1" t="inlineStr"/>
     </row>
-    <row r="61" ht="107" customHeight="1">
+    <row r="61" ht="32" customHeight="1">
       <c r="A61" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5792,7 +5792,7 @@
       <c r="J61" s="1" t="inlineStr"/>
       <c r="K61" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#001；位置：L001-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L61" s="1" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="V61" s="1" t="inlineStr"/>
     </row>
-    <row r="62" ht="107" customHeight="1">
+    <row r="62" ht="32" customHeight="1">
       <c r="A62" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5880,7 +5880,7 @@
       <c r="J62" s="1" t="inlineStr"/>
       <c r="K62" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#002；位置：L002-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L62" s="1" t="inlineStr">
@@ -5929,7 +5929,7 @@
       </c>
       <c r="V62" s="1" t="inlineStr"/>
     </row>
-    <row r="63" ht="107" customHeight="1">
+    <row r="63" ht="32" customHeight="1">
       <c r="A63" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -5968,7 +5968,7 @@
       <c r="J63" s="1" t="inlineStr"/>
       <c r="K63" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#003；位置：L003-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L63" s="1" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="V63" s="1" t="inlineStr"/>
     </row>
-    <row r="64" ht="107" customHeight="1">
+    <row r="64" ht="32" customHeight="1">
       <c r="A64" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6056,7 +6056,7 @@
       <c r="J64" s="1" t="inlineStr"/>
       <c r="K64" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#004；位置：L004-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L64" s="1" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="V64" s="1" t="inlineStr"/>
     </row>
-    <row r="65" ht="107" customHeight="1">
+    <row r="65" ht="32" customHeight="1">
       <c r="A65" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6144,7 +6144,7 @@
       <c r="J65" s="1" t="inlineStr"/>
       <c r="K65" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#005；位置：L005-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L65" s="1" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="V65" s="1" t="inlineStr"/>
     </row>
-    <row r="66" ht="107" customHeight="1">
+    <row r="66" ht="32" customHeight="1">
       <c r="A66" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6232,7 +6232,7 @@
       <c r="J66" s="1" t="inlineStr"/>
       <c r="K66" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#006；位置：L006-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L66" s="1" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="V66" s="1" t="inlineStr"/>
     </row>
-    <row r="67" ht="107" customHeight="1">
+    <row r="67" ht="32" customHeight="1">
       <c r="A67" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6320,7 +6320,7 @@
       <c r="J67" s="1" t="inlineStr"/>
       <c r="K67" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#007；位置：L007-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L67" s="1" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="V67" s="1" t="inlineStr"/>
     </row>
-    <row r="68" ht="107" customHeight="1">
+    <row r="68" ht="32" customHeight="1">
       <c r="A68" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6408,7 +6408,7 @@
       <c r="J68" s="1" t="inlineStr"/>
       <c r="K68" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#008；位置：L008-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L68" s="1" t="inlineStr">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="V68" s="1" t="inlineStr"/>
     </row>
-    <row r="69" ht="107" customHeight="1">
+    <row r="69" ht="32" customHeight="1">
       <c r="A69" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6496,7 +6496,7 @@
       <c r="J69" s="1" t="inlineStr"/>
       <c r="K69" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#009；位置：L009-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L69" s="1" t="inlineStr">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="V69" s="1" t="inlineStr"/>
     </row>
-    <row r="70" ht="107" customHeight="1">
+    <row r="70" ht="32" customHeight="1">
       <c r="A70" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6584,7 +6584,7 @@
       <c r="J70" s="1" t="inlineStr"/>
       <c r="K70" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#010；位置：L010-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L70" s="1" t="inlineStr">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="V70" s="1" t="inlineStr"/>
     </row>
-    <row r="71" ht="107" customHeight="1">
+    <row r="71" ht="32" customHeight="1">
       <c r="A71" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6672,7 +6672,7 @@
       <c r="J71" s="1" t="inlineStr"/>
       <c r="K71" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#011；位置：L011-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L71" s="1" t="inlineStr">
@@ -6721,7 +6721,7 @@
       </c>
       <c r="V71" s="1" t="inlineStr"/>
     </row>
-    <row r="72" ht="107" customHeight="1">
+    <row r="72" ht="32" customHeight="1">
       <c r="A72" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6760,7 +6760,7 @@
       <c r="J72" s="1" t="inlineStr"/>
       <c r="K72" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#012；位置：L012-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L72" s="1" t="inlineStr">
@@ -6809,7 +6809,7 @@
       </c>
       <c r="V72" s="1" t="inlineStr"/>
     </row>
-    <row r="73" ht="107" customHeight="1">
+    <row r="73" ht="32" customHeight="1">
       <c r="A73" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6848,7 +6848,7 @@
       <c r="J73" s="1" t="inlineStr"/>
       <c r="K73" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#013；位置：L013-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L73" s="1" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="V73" s="1" t="inlineStr"/>
     </row>
-    <row r="74" ht="107" customHeight="1">
+    <row r="74" ht="32" customHeight="1">
       <c r="A74" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -6936,7 +6936,7 @@
       <c r="J74" s="1" t="inlineStr"/>
       <c r="K74" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#014；位置：L014-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L74" s="1" t="inlineStr">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="V74" s="1" t="inlineStr"/>
     </row>
-    <row r="75" ht="107" customHeight="1">
+    <row r="75" ht="32" customHeight="1">
       <c r="A75" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7024,7 +7024,7 @@
       <c r="J75" s="1" t="inlineStr"/>
       <c r="K75" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#015；位置：L015-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L75" s="1" t="inlineStr">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="V75" s="1" t="inlineStr"/>
     </row>
-    <row r="76" ht="107" customHeight="1">
+    <row r="76" ht="32" customHeight="1">
       <c r="A76" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7112,7 +7112,7 @@
       <c r="J76" s="1" t="inlineStr"/>
       <c r="K76" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#016；位置：L016-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L76" s="1" t="inlineStr">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="V76" s="1" t="inlineStr"/>
     </row>
-    <row r="77" ht="107" customHeight="1">
+    <row r="77" ht="32" customHeight="1">
       <c r="A77" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7200,7 +7200,7 @@
       <c r="J77" s="1" t="inlineStr"/>
       <c r="K77" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#017；位置：L017-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L77" s="1" t="inlineStr">
@@ -7249,7 +7249,7 @@
       </c>
       <c r="V77" s="1" t="inlineStr"/>
     </row>
-    <row r="78" ht="107" customHeight="1">
+    <row r="78" ht="32" customHeight="1">
       <c r="A78" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7288,7 +7288,7 @@
       <c r="J78" s="1" t="inlineStr"/>
       <c r="K78" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#018；位置：L018-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L78" s="1" t="inlineStr">
@@ -7337,7 +7337,7 @@
       </c>
       <c r="V78" s="1" t="inlineStr"/>
     </row>
-    <row r="79" ht="107" customHeight="1">
+    <row r="79" ht="32" customHeight="1">
       <c r="A79" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7376,7 +7376,7 @@
       <c r="J79" s="1" t="inlineStr"/>
       <c r="K79" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#019；位置：L019-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L79" s="1" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="V79" s="1" t="inlineStr"/>
     </row>
-    <row r="80" ht="107" customHeight="1">
+    <row r="80" ht="32" customHeight="1">
       <c r="A80" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7464,7 +7464,7 @@
       <c r="J80" s="1" t="inlineStr"/>
       <c r="K80" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#020；位置：L020-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L80" s="1" t="inlineStr">
@@ -7513,7 +7513,7 @@
       </c>
       <c r="V80" s="1" t="inlineStr"/>
     </row>
-    <row r="81" ht="107" customHeight="1">
+    <row r="81" ht="32" customHeight="1">
       <c r="A81" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7552,7 +7552,7 @@
       <c r="J81" s="1" t="inlineStr"/>
       <c r="K81" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#021；位置：L021-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L81" s="1" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="V81" s="1" t="inlineStr"/>
     </row>
-    <row r="82" ht="107" customHeight="1">
+    <row r="82" ht="32" customHeight="1">
       <c r="A82" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7640,7 +7640,7 @@
       <c r="J82" s="1" t="inlineStr"/>
       <c r="K82" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#022；位置：L022-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L82" s="1" t="inlineStr">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="V82" s="1" t="inlineStr"/>
     </row>
-    <row r="83" ht="107" customHeight="1">
+    <row r="83" ht="32" customHeight="1">
       <c r="A83" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7728,7 +7728,7 @@
       <c r="J83" s="1" t="inlineStr"/>
       <c r="K83" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#023；位置：L023-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L83" s="1" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="V83" s="1" t="inlineStr"/>
     </row>
-    <row r="84" ht="107" customHeight="1">
+    <row r="84" ht="32" customHeight="1">
       <c r="A84" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7816,7 +7816,7 @@
       <c r="J84" s="1" t="inlineStr"/>
       <c r="K84" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#024；位置：L024-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L84" s="1" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="V84" s="1" t="inlineStr"/>
     </row>
-    <row r="85" ht="107" customHeight="1">
+    <row r="85" ht="32" customHeight="1">
       <c r="A85" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7904,7 +7904,7 @@
       <c r="J85" s="1" t="inlineStr"/>
       <c r="K85" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#025；位置：L025-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L85" s="1" t="inlineStr">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="V85" s="1" t="inlineStr"/>
     </row>
-    <row r="86" ht="107" customHeight="1">
+    <row r="86" ht="32" customHeight="1">
       <c r="A86" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -7992,7 +7992,7 @@
       <c r="J86" s="1" t="inlineStr"/>
       <c r="K86" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#026；位置：L026-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L86" s="1" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="V86" s="1" t="inlineStr"/>
     </row>
-    <row r="87" ht="107" customHeight="1">
+    <row r="87" ht="32" customHeight="1">
       <c r="A87" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8080,7 +8080,7 @@
       <c r="J87" s="1" t="inlineStr"/>
       <c r="K87" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#027；位置：L027-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L87" s="1" t="inlineStr">
@@ -8129,7 +8129,7 @@
       </c>
       <c r="V87" s="1" t="inlineStr"/>
     </row>
-    <row r="88" ht="107" customHeight="1">
+    <row r="88" ht="32" customHeight="1">
       <c r="A88" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8168,7 +8168,7 @@
       <c r="J88" s="1" t="inlineStr"/>
       <c r="K88" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#028；位置：L028-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L88" s="1" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="V88" s="1" t="inlineStr"/>
     </row>
-    <row r="89" ht="107" customHeight="1">
+    <row r="89" ht="32" customHeight="1">
       <c r="A89" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8256,7 +8256,7 @@
       <c r="J89" s="1" t="inlineStr"/>
       <c r="K89" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#029；位置：L029-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L89" s="1" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="V89" s="1" t="inlineStr"/>
     </row>
-    <row r="90" ht="107" customHeight="1">
+    <row r="90" ht="32" customHeight="1">
       <c r="A90" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8344,7 +8344,7 @@
       <c r="J90" s="1" t="inlineStr"/>
       <c r="K90" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#030；位置：L030-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L90" s="1" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="V90" s="1" t="inlineStr"/>
     </row>
-    <row r="91" ht="107" customHeight="1">
+    <row r="91" ht="32" customHeight="1">
       <c r="A91" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8432,7 +8432,7 @@
       <c r="J91" s="1" t="inlineStr"/>
       <c r="K91" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#031；位置：L031-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L91" s="1" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="V91" s="1" t="inlineStr"/>
     </row>
-    <row r="92" ht="107" customHeight="1">
+    <row r="92" ht="32" customHeight="1">
       <c r="A92" s="1" t="inlineStr">
         <is>
           <t>事件</t>
@@ -8520,7 +8520,7 @@
       <c r="J92" s="1" t="inlineStr"/>
       <c r="K92" s="1" t="inlineStr">
         <is>
-          <t>批次：2026年1号机C修；日期精度=月，日未提供（月份为用户确认的检修月份）；来源ID：2026年1号机C修!R39#032；位置：L032-F024；源位置：1-32屏的炉后第1根共32个弯头；方法：射线；结果：合格；结果性质：原文合格；由源汇总行展开，非新增检测；已包含在本版全部批次文件；用户已确认高过每屏24根（F001–F024↔B024–B001）：源“炉后第1根”≙F024，编码落规范方向F</t>
+          <t>方法：射线；结果：合格</t>
         </is>
       </c>
       <c r="L92" s="1" t="inlineStr">
